--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:46</t>
+          <t>2026-09-07 20:13:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:48</t>
+          <t>2026-09-07 20:13:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81278</v>
+        <v>4.81294</v>
       </c>
       <c r="G3" t="n">
-        <v>13332</v>
+        <v>13343</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>267</v>
       </c>
       <c r="R3" t="n">
-        <v>12399</v>
+        <v>12409</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:50</t>
+          <t>2026-09-07 20:13:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87598</v>
+        <v>3.8768</v>
       </c>
       <c r="G4" t="n">
         <v>4854</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:53</t>
+          <t>2026-09-07 20:13:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85428</v>
+        <v>2.85507</v>
       </c>
       <c r="G5" t="n">
-        <v>3095</v>
+        <v>3098</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="O5" t="n">
         <v>155</v>
@@ -805,7 +805,7 @@
         <v>124</v>
       </c>
       <c r="R5" t="n">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:55</t>
+          <t>2026-09-07 20:13:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:57</t>
+          <t>2026-09-07 20:13:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:00</t>
+          <t>2026-09-07 20:13:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:02</t>
+          <t>2026-09-07 20:13:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:04</t>
+          <t>2026-09-07 20:13:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:07</t>
+          <t>2026-09-07 20:13:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:09</t>
+          <t>2026-09-07 20:13:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70901</v>
+        <v>4.71049</v>
       </c>
       <c r="G12" t="n">
-        <v>3086</v>
+        <v>3088</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O12" t="n">
         <v>31</v>
@@ -1309,7 +1309,7 @@
         <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>2685</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:12</t>
+          <t>2026-09-07 20:13:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00521</v>
+        <v>4.00347</v>
       </c>
       <c r="G13" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O13" t="n">
         <v>23</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:14</t>
+          <t>2026-09-07 20:13:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.51029</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:17</t>
+          <t>2026-09-07 20:13:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-06 18:42:19</t>
+          <t>2026-09-07 20:13:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74164</v>
+        <v>4.74181</v>
       </c>
       <c r="G16" t="n">
-        <v>32462</v>
+        <v>32481</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="O16" t="n">
         <v>325</v>
       </c>
       <c r="P16" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Q16" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="R16" t="n">
-        <v>28891</v>
+        <v>28908</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:09</t>
+          <t>2026-09-08 19:39:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:11</t>
+          <t>2026-09-08 19:39:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81294</v>
+        <v>4.81306</v>
       </c>
       <c r="G3" t="n">
-        <v>13343</v>
+        <v>13352</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q3" t="n">
         <v>267</v>
       </c>
       <c r="R3" t="n">
-        <v>12409</v>
+        <v>12417</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:14</t>
+          <t>2026-09-08 19:39:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.1</t>
+          <t>2.22.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>August 18, 2026</t>
+          <t>September 08, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:17</t>
+          <t>2026-09-08 19:39:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85507</v>
+        <v>2.85447</v>
       </c>
       <c r="G5" t="n">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="O5" t="n">
         <v>155</v>
@@ -805,7 +805,7 @@
         <v>124</v>
       </c>
       <c r="R5" t="n">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:19</t>
+          <t>2026-09-08 19:39:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:21</t>
+          <t>2026-09-08 19:39:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98439</v>
+        <v>3.98493</v>
       </c>
       <c r="G7" t="n">
-        <v>3779</v>
+        <v>3782</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O7" t="n">
         <v>151</v>
@@ -949,7 +949,7 @@
         <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>2381</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:24</t>
+          <t>2026-09-08 19:39:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:26</t>
+          <t>2026-09-08 19:39:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:29</t>
+          <t>2026-09-08 19:39:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:31</t>
+          <t>2026-09-08 19:39:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:33</t>
+          <t>2026-09-08 19:39:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71049</v>
+        <v>4.71035</v>
       </c>
       <c r="G12" t="n">
-        <v>3088</v>
+        <v>3090</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>2717</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:36</t>
+          <t>2026-09-08 19:39:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:38</t>
+          <t>2026-09-08 19:39:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:41</t>
+          <t>2026-09-08 19:39:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:43</t>
+          <t>2026-09-08 19:39:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74181</v>
+        <v>4.74202</v>
       </c>
       <c r="G16" t="n">
-        <v>32481</v>
+        <v>32499</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="O16" t="n">
         <v>325</v>
@@ -1594,10 +1594,10 @@
         <v>650</v>
       </c>
       <c r="Q16" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="R16" t="n">
-        <v>28908</v>
+        <v>28924</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:06</t>
+          <t>2026-09-09 19:33:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:08</t>
+          <t>2026-09-09 19:33:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81306</v>
+        <v>4.81299</v>
       </c>
       <c r="G3" t="n">
-        <v>13352</v>
+        <v>13363</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>267</v>
       </c>
       <c r="R3" t="n">
-        <v>12417</v>
+        <v>12428</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:10</t>
+          <t>2026-09-09 19:33:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:13</t>
+          <t>2026-09-09 19:33:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85447</v>
+        <v>2.85585</v>
       </c>
       <c r="G5" t="n">
-        <v>3099</v>
+        <v>3101</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:15</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:18</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98493</v>
+        <v>3.9852</v>
       </c>
       <c r="G7" t="n">
-        <v>3782</v>
+        <v>3783</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:20</t>
+          <t>2026-09-09 19:33:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74217</v>
+        <v>4.74218</v>
       </c>
       <c r="G8" t="n">
-        <v>13625</v>
+        <v>13626</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12126</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:22</t>
+          <t>2026-09-09 19:33:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:25</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:27</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.65217</v>
+        <v>2.66667</v>
       </c>
       <c r="G11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:29</t>
+          <t>2026-09-09 19:33:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71035</v>
+        <v>4.71128</v>
       </c>
       <c r="G12" t="n">
-        <v>3090</v>
+        <v>3093</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>62</v>
       </c>
       <c r="Q12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2719</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:32</t>
+          <t>2026-09-09 19:33:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:34</t>
+          <t>2026-09-09 19:33:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:37</t>
+          <t>2026-09-09 19:34:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:39</t>
+          <t>2026-09-09 19:34:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74202</v>
+        <v>4.74218</v>
       </c>
       <c r="G16" t="n">
-        <v>32499</v>
+        <v>32511</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1300</v>
       </c>
       <c r="R16" t="n">
-        <v>28924</v>
+        <v>28935</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:30</t>
+          <t>2026-09-10 19:19:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:32</t>
+          <t>2026-09-10 19:19:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81299</v>
+        <v>4.81229</v>
       </c>
       <c r="G3" t="n">
-        <v>13363</v>
+        <v>13372</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>267</v>
       </c>
       <c r="R3" t="n">
-        <v>12428</v>
+        <v>12436</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:35</t>
+          <t>2026-09-10 19:20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.8768</v>
+        <v>3.87621</v>
       </c>
       <c r="G4" t="n">
-        <v>4854</v>
+        <v>4855</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3009</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:37</t>
+          <t>2026-09-10 19:20:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85585</v>
+        <v>2.85949</v>
       </c>
       <c r="G5" t="n">
-        <v>3101</v>
+        <v>3110</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="O5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P5" t="n">
         <v>93</v>
@@ -805,7 +805,7 @@
         <v>124</v>
       </c>
       <c r="R5" t="n">
-        <v>1271</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-10 19:20:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.13725</v>
+        <v>3.12338</v>
       </c>
       <c r="G6" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-10 19:20:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:44</t>
+          <t>2026-09-10 19:20:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:46</t>
+          <t>2026-09-10 19:20:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-10 19:20:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-10 19:20:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66667</v>
+        <v>2.6383</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:53</t>
+          <t>2026-09-10 19:20:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71128</v>
+        <v>4.71138</v>
       </c>
       <c r="G12" t="n">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2722</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:56</t>
+          <t>2026-09-10 19:20:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:58</t>
+          <t>2026-09-10 19:20:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:01</t>
+          <t>2026-09-10 19:20:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:03</t>
+          <t>2026-09-10 19:20:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74218</v>
+        <v>4.74224</v>
       </c>
       <c r="G16" t="n">
-        <v>32511</v>
+        <v>32526</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="O16" t="n">
         <v>325</v>
       </c>
       <c r="P16" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Q16" t="n">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="R16" t="n">
-        <v>28935</v>
+        <v>28948</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:55</t>
+          <t>2026-09-11 19:20:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:57</t>
+          <t>2026-09-11 19:21:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81229</v>
+        <v>4.81235</v>
       </c>
       <c r="G3" t="n">
-        <v>13372</v>
+        <v>13381</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.45.1</t>
+          <t>4.46.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>August 29, 2026</t>
+          <t>September 11, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -658,10 +658,10 @@
         <v>134</v>
       </c>
       <c r="Q3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R3" t="n">
-        <v>12436</v>
+        <v>12444</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:00</t>
+          <t>2026-09-11 19:21:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87621</v>
+        <v>3.87598</v>
       </c>
       <c r="G4" t="n">
-        <v>4855</v>
+        <v>4854</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3010</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:02</t>
+          <t>2026-09-11 19:21:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85949</v>
+        <v>2.85889</v>
       </c>
       <c r="G5" t="n">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>124</v>
       </c>
       <c r="R5" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:05</t>
+          <t>2026-09-11 19:21:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:07</t>
+          <t>2026-09-11 19:21:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9852</v>
+        <v>3.98547</v>
       </c>
       <c r="G7" t="n">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>2383</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:09</t>
+          <t>2026-09-11 19:21:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:12</t>
+          <t>2026-09-11 19:21:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:14</t>
+          <t>2026-09-11 19:21:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.88324</v>
+        <v>3.88429</v>
       </c>
       <c r="G10" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1156,16 +1156,16 @@
         <v>234</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="n">
         <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:17</t>
+          <t>2026-09-11 19:21:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:19</t>
+          <t>2026-09-11 19:21:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71138</v>
+        <v>4.71156</v>
       </c>
       <c r="G12" t="n">
-        <v>3094</v>
+        <v>3096</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>September 02, 2026</t>
+          <t>September 11, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2723</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:22</t>
+          <t>2026-09-11 19:21:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:24</t>
+          <t>2026-09-11 19:21:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:26</t>
+          <t>2026-09-11 19:21:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-10 19:20:29</t>
+          <t>2026-09-11 19:21:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74224</v>
+        <v>4.74221</v>
       </c>
       <c r="G16" t="n">
-        <v>32526</v>
+        <v>32535</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1301</v>
       </c>
       <c r="R16" t="n">
-        <v>28948</v>
+        <v>28956</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:58</t>
+          <t>2026-09-13 19:01:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:01</t>
+          <t>2026-09-13 19:01:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81235</v>
+        <v>4.81257</v>
       </c>
       <c r="G3" t="n">
-        <v>13381</v>
+        <v>13402</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O3" t="n">
         <v>134</v>
@@ -661,7 +661,7 @@
         <v>268</v>
       </c>
       <c r="R3" t="n">
-        <v>12444</v>
+        <v>12464</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:03</t>
+          <t>2026-09-13 19:01:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87598</v>
+        <v>3.87557</v>
       </c>
       <c r="G4" t="n">
         <v>4854</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:06</t>
+          <t>2026-09-13 19:02:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85889</v>
+        <v>2.85898</v>
       </c>
       <c r="G5" t="n">
-        <v>3111</v>
+        <v>3113</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="O5" t="n">
         <v>156</v>
@@ -802,7 +802,7 @@
         <v>93</v>
       </c>
       <c r="Q5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R5" t="n">
         <v>1276</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:08</t>
+          <t>2026-09-13 19:02:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.12338</v>
+        <v>3.17791</v>
       </c>
       <c r="G6" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -861,23 +861,23 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>April 05, 2026</t>
+          <t>September 12, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:11</t>
+          <t>2026-09-13 19:02:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:13</t>
+          <t>2026-09-13 19:02:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74218</v>
+        <v>4.74193</v>
       </c>
       <c r="G8" t="n">
-        <v>13626</v>
+        <v>13628</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12127</v>
+        <v>12129</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:16</t>
+          <t>2026-09-13 19:02:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:18</t>
+          <t>2026-09-13 19:02:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:20</t>
+          <t>2026-09-13 19:02:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:23</t>
+          <t>2026-09-13 19:02:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71156</v>
+        <v>4.70934</v>
       </c>
       <c r="G12" t="n">
-        <v>3096</v>
+        <v>3100</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2724</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:25</t>
+          <t>2026-09-13 19:02:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00347</v>
+        <v>4.00173</v>
       </c>
       <c r="G13" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:28</t>
+          <t>2026-09-13 19:02:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:30</t>
+          <t>2026-09-13 19:02:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:32</t>
+          <t>2026-09-13 19:02:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74221</v>
+        <v>4.74165</v>
       </c>
       <c r="G16" t="n">
-        <v>32535</v>
+        <v>32549</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="O16" t="n">
         <v>325</v>
@@ -1594,10 +1594,10 @@
         <v>651</v>
       </c>
       <c r="Q16" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="R16" t="n">
-        <v>28956</v>
+        <v>28969</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:54</t>
+          <t>2026-09-14 20:40:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:56</t>
+          <t>2026-09-14 20:40:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81257</v>
+        <v>4.81267</v>
       </c>
       <c r="G3" t="n">
-        <v>13402</v>
+        <v>13415</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>268</v>
       </c>
       <c r="R3" t="n">
-        <v>12464</v>
+        <v>12476</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:59</t>
+          <t>2026-09-14 20:40:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87557</v>
+        <v>3.87603</v>
       </c>
       <c r="G4" t="n">
-        <v>4854</v>
+        <v>4856</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3009</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:01</t>
+          <t>2026-09-14 20:40:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85898</v>
+        <v>2.85967</v>
       </c>
       <c r="G5" t="n">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.6.6</t>
+          <t>10.6.7</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -789,11 +789,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>July 05, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="O5" t="n">
         <v>156</v>
@@ -805,7 +805,7 @@
         <v>125</v>
       </c>
       <c r="R5" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:03</t>
+          <t>2026-09-14 20:40:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.17791</v>
+        <v>3.22941</v>
       </c>
       <c r="G6" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:06</t>
+          <t>2026-09-14 20:40:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98547</v>
+        <v>3.98573</v>
       </c>
       <c r="G7" t="n">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:08</t>
+          <t>2026-09-14 20:40:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:10</t>
+          <t>2026-09-14 20:40:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:13</t>
+          <t>2026-09-14 20:40:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:15</t>
+          <t>2026-09-14 20:40:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:17</t>
+          <t>2026-09-14 20:40:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70934</v>
+        <v>4.70858</v>
       </c>
       <c r="G12" t="n">
-        <v>3100</v>
+        <v>3102</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2697</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:20</t>
+          <t>2026-09-14 20:40:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00173</v>
+        <v>4.00345</v>
       </c>
       <c r="G13" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.8.1</t>
+          <t>1.8.2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>September 01, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:22</t>
+          <t>2026-09-14 20:40:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:24</t>
+          <t>2026-09-14 20:41:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-13 19:02:27</t>
+          <t>2026-09-14 20:41:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74165</v>
+        <v>4.74177</v>
       </c>
       <c r="G16" t="n">
-        <v>32549</v>
+        <v>32568</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.5</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,23 +1581,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>August 12, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="O16" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P16" t="n">
         <v>651</v>
       </c>
       <c r="Q16" t="n">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="R16" t="n">
-        <v>28969</v>
+        <v>28986</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:27</t>
+          <t>2026-09-15 19:54:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:29</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81267</v>
+        <v>4.81273</v>
       </c>
       <c r="G3" t="n">
-        <v>13415</v>
+        <v>13419</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O3" t="n">
         <v>134</v>
@@ -661,7 +661,7 @@
         <v>268</v>
       </c>
       <c r="R3" t="n">
-        <v>12476</v>
+        <v>12480</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:32</t>
+          <t>2026-09-15 19:54:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87603</v>
+        <v>3.87626</v>
       </c>
       <c r="G4" t="n">
-        <v>4856</v>
+        <v>4857</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>243</v>
       </c>
       <c r="Q4" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="R4" t="n">
         <v>3011</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:34</t>
+          <t>2026-09-15 19:54:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.6.7</t>
+          <t>10.6.8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>September 14, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:37</t>
+          <t>2026-09-15 19:54:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.22941</v>
+        <v>3.23977</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>September 12, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -871,13 +871,13 @@
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:40</t>
+          <t>2026-09-15 19:54:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98573</v>
+        <v>3.98494</v>
       </c>
       <c r="G7" t="n">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>2383</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:43</t>
+          <t>2026-09-15 19:54:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74193</v>
+        <v>4.74191</v>
       </c>
       <c r="G8" t="n">
-        <v>13628</v>
+        <v>13627</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12129</v>
+        <v>12128</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:45</t>
+          <t>2026-09-15 19:54:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:47</t>
+          <t>2026-09-15 19:54:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:50</t>
+          <t>2026-09-15 19:54:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:53</t>
+          <t>2026-09-15 19:54:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70858</v>
+        <v>4.70824</v>
       </c>
       <c r="G12" t="n">
         <v>3102</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>September 11, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:55</t>
+          <t>2026-09-15 19:54:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00345</v>
+        <v>4.00173</v>
       </c>
       <c r="G13" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:58</t>
+          <t>2026-09-15 19:54:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14 20:41:01</t>
+          <t>2026-09-15 19:54:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14 20:41:03</t>
+          <t>2026-09-15 19:54:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74177</v>
+        <v>4.74146</v>
       </c>
       <c r="G16" t="n">
-        <v>32568</v>
+        <v>32576</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>326</v>
       </c>
       <c r="P16" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Q16" t="n">
         <v>1303</v>
       </c>
       <c r="R16" t="n">
-        <v>28986</v>
+        <v>28993</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:04</t>
+          <t>2026-09-16 19:47:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-16 19:47:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81273</v>
+        <v>4.81288</v>
       </c>
       <c r="G3" t="n">
-        <v>13419</v>
+        <v>13430</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.0</t>
+          <t>4.46.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>September 11, 2026</t>
+          <t>September 16, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -658,10 +658,10 @@
         <v>134</v>
       </c>
       <c r="Q3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R3" t="n">
-        <v>12480</v>
+        <v>12490</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:09</t>
+          <t>2026-09-16 19:47:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:11</t>
+          <t>2026-09-16 19:47:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85967</v>
+        <v>2.86186</v>
       </c>
       <c r="G5" t="n">
-        <v>3114</v>
+        <v>3120</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="O5" t="n">
         <v>156</v>
       </c>
       <c r="P5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q5" t="n">
         <v>125</v>
       </c>
       <c r="R5" t="n">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:13</t>
+          <t>2026-09-16 19:47:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -874,10 +874,10 @@
         <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:16</t>
+          <t>2026-09-16 19:47:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:18</t>
+          <t>2026-09-16 19:47:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:21</t>
+          <t>2026-09-16 19:47:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:24</t>
+          <t>2026-09-16 19:47:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:26</t>
+          <t>2026-09-16 19:47:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:28</t>
+          <t>2026-09-16 19:47:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2699</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:31</t>
+          <t>2026-09-16 19:47:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:33</t>
+          <t>2026-09-16 19:47:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:35</t>
+          <t>2026-09-16 19:47:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:38</t>
+          <t>2026-09-16 19:47:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:25</t>
+          <t>2026-09-17 19:56:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:27</t>
+          <t>2026-09-17 19:56:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81288</v>
+        <v>4.81292</v>
       </c>
       <c r="G3" t="n">
-        <v>13430</v>
+        <v>13438</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>269</v>
       </c>
       <c r="R3" t="n">
-        <v>12490</v>
+        <v>12497</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:29</t>
+          <t>2026-09-17 19:56:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87626</v>
+        <v>3.87631</v>
       </c>
       <c r="G4" t="n">
-        <v>4857</v>
+        <v>4859</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="O4" t="n">
         <v>243</v>
@@ -733,7 +733,7 @@
         <v>389</v>
       </c>
       <c r="R4" t="n">
-        <v>3011</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:32</t>
+          <t>2026-09-17 19:56:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86186</v>
+        <v>2.85423</v>
       </c>
       <c r="G5" t="n">
-        <v>3120</v>
+        <v>3135</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="O5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>94</v>
@@ -805,7 +805,7 @@
         <v>125</v>
       </c>
       <c r="R5" t="n">
-        <v>1279</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:34</t>
+          <t>2026-09-17 19:56:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.23977</v>
+        <v>3.26519</v>
       </c>
       <c r="G6" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:36</t>
+          <t>2026-09-17 19:56:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>September 02, 2026</t>
+          <t>September 16, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:38</t>
+          <t>2026-09-17 19:56:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:40</t>
+          <t>2026-09-17 19:56:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:42</t>
+          <t>2026-09-17 19:56:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:44</t>
+          <t>2026-09-17 19:56:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:47</t>
+          <t>2026-09-17 19:56:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70824</v>
+        <v>4.71014</v>
       </c>
       <c r="G12" t="n">
-        <v>3102</v>
+        <v>3105</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2730</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:49</t>
+          <t>2026-09-17 19:56:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:51</t>
+          <t>2026-09-17 19:56:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.51029</v>
       </c>
       <c r="G14" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:53</t>
+          <t>2026-09-17 19:56:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:55</t>
+          <t>2026-09-17 19:56:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74146</v>
+        <v>4.7413</v>
       </c>
       <c r="G16" t="n">
-        <v>32576</v>
+        <v>32598</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="O16" t="n">
         <v>326</v>
@@ -1594,10 +1594,10 @@
         <v>652</v>
       </c>
       <c r="Q16" t="n">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="R16" t="n">
-        <v>28993</v>
+        <v>29012</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:25</t>
+          <t>2026-09-18 19:16:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:27</t>
+          <t>2026-09-18 19:16:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81292</v>
+        <v>4.81283</v>
       </c>
       <c r="G3" t="n">
-        <v>13438</v>
+        <v>13448</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.1</t>
+          <t>4.46.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>September 16, 2026</t>
+          <t>September 17, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -661,7 +661,7 @@
         <v>269</v>
       </c>
       <c r="R3" t="n">
-        <v>12497</v>
+        <v>12507</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:30</t>
+          <t>2026-09-18 19:16:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:32</t>
+          <t>2026-09-18 19:16:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85423</v>
+        <v>2.85225</v>
       </c>
       <c r="G5" t="n">
-        <v>3135</v>
+        <v>3154</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1473</v>
+        <v>1482</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R5" t="n">
-        <v>1285</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:34</t>
+          <t>2026-09-18 19:16:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.26519</v>
+        <v>3.28415</v>
       </c>
       <c r="G6" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -874,10 +874,10 @@
         <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:37</t>
+          <t>2026-09-18 19:16:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98494</v>
+        <v>3.98468</v>
       </c>
       <c r="G7" t="n">
-        <v>3784</v>
+        <v>3787</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O7" t="n">
         <v>151</v>
@@ -946,10 +946,10 @@
         <v>189</v>
       </c>
       <c r="Q7" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="R7" t="n">
-        <v>2384</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:39</t>
+          <t>2026-09-18 19:16:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:41</t>
+          <t>2026-09-18 19:16:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:43</t>
+          <t>2026-09-18 19:16:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:46</t>
+          <t>2026-09-18 19:16:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:49</t>
+          <t>2026-09-18 19:16:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71014</v>
+        <v>4.70904</v>
       </c>
       <c r="G12" t="n">
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2701</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:51</t>
+          <t>2026-09-18 19:16:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00173</v>
+        <v>4.00345</v>
       </c>
       <c r="G13" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:53</t>
+          <t>2026-09-18 19:17:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.51029</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:55</t>
+          <t>2026-09-18 19:17:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:57</t>
+          <t>2026-09-18 19:17:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7413</v>
+        <v>4.74132</v>
       </c>
       <c r="G16" t="n">
-        <v>32598</v>
+        <v>32608</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1304</v>
       </c>
       <c r="R16" t="n">
-        <v>29012</v>
+        <v>29021</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:32</t>
+          <t>2026-09-19 19:02:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:34</t>
+          <t>2026-09-19 19:02:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -622,7 +622,7 @@
         <v>4.81283</v>
       </c>
       <c r="G3" t="n">
-        <v>13448</v>
+        <v>13454</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q3" t="n">
         <v>269</v>
       </c>
       <c r="R3" t="n">
-        <v>12507</v>
+        <v>12512</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:37</t>
+          <t>2026-09-19 19:02:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:39</t>
+          <t>2026-09-19 19:02:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85225</v>
+        <v>2.8537</v>
       </c>
       <c r="G5" t="n">
-        <v>3154</v>
+        <v>3158</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="O5" t="n">
         <v>158</v>
@@ -805,7 +805,7 @@
         <v>126</v>
       </c>
       <c r="R5" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:42</t>
+          <t>2026-09-19 19:02:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.28415</v>
+        <v>3.29348</v>
       </c>
       <c r="G6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -877,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:44</t>
+          <t>2026-09-19 19:02:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:47</t>
+          <t>2026-09-19 19:02:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:49</t>
+          <t>2026-09-19 19:02:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:52</t>
+          <t>2026-09-19 19:02:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:54</t>
+          <t>2026-09-19 19:02:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:57</t>
+          <t>2026-09-19 19:02:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70904</v>
+        <v>4.70913</v>
       </c>
       <c r="G12" t="n">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="R12" t="n">
-        <v>2703</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:59</t>
+          <t>2026-09-19 19:02:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-18 19:17:02</t>
+          <t>2026-09-19 19:02:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-18 19:17:04</t>
+          <t>2026-09-19 19:02:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-18 19:17:07</t>
+          <t>2026-09-19 19:02:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74132</v>
+        <v>4.74139</v>
       </c>
       <c r="G16" t="n">
-        <v>32608</v>
+        <v>32620</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="O16" t="n">
         <v>326</v>
@@ -1594,10 +1594,10 @@
         <v>652</v>
       </c>
       <c r="Q16" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="R16" t="n">
-        <v>29021</v>
+        <v>29032</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:04</t>
+          <t>2026-09-20 19:07:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>September 20, 2026</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:07</t>
+          <t>2026-09-20 19:07:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81283</v>
+        <v>4.81263</v>
       </c>
       <c r="G3" t="n">
-        <v>13454</v>
+        <v>13465</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>269</v>
       </c>
       <c r="R3" t="n">
-        <v>12512</v>
+        <v>12522</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:09</t>
+          <t>2026-09-20 19:07:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:11</t>
+          <t>2026-09-20 19:07:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8537</v>
+        <v>2.85248</v>
       </c>
       <c r="G5" t="n">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="O5" t="n">
         <v>158</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:13</t>
+          <t>2026-09-20 19:07:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.29348</v>
+        <v>3.3027</v>
       </c>
       <c r="G6" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:15</t>
+          <t>2026-09-20 19:07:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98468</v>
+        <v>3.9839</v>
       </c>
       <c r="G7" t="n">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>644</v>
       </c>
       <c r="O7" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P7" t="n">
         <v>189</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:18</t>
+          <t>2026-09-20 19:07:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:20</t>
+          <t>2026-09-20 19:07:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:22</t>
+          <t>2026-09-20 19:07:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:24</t>
+          <t>2026-09-20 19:07:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6383</v>
+        <v>2.59184</v>
       </c>
       <c r="G11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:26</t>
+          <t>2026-09-20 19:07:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70913</v>
+        <v>4.70803</v>
       </c>
       <c r="G12" t="n">
-        <v>3108</v>
+        <v>3110</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>62</v>
       </c>
       <c r="Q12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R12" t="n">
-        <v>2704</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:28</t>
+          <t>2026-09-20 19:07:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:31</t>
+          <t>2026-09-20 19:07:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>July 14, 2026</t>
+          <t>September 20, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:33</t>
+          <t>2026-09-20 19:07:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:35</t>
+          <t>2026-09-20 19:07:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74139</v>
+        <v>4.74118</v>
       </c>
       <c r="G16" t="n">
-        <v>32620</v>
+        <v>32626</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>326</v>
       </c>
       <c r="P16" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="Q16" t="n">
         <v>1305</v>
       </c>
       <c r="R16" t="n">
-        <v>29032</v>
+        <v>29037</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:06</t>
+          <t>2026-09-21 20:41:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:08</t>
+          <t>2026-09-21 20:41:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -622,7 +622,7 @@
         <v>4.81263</v>
       </c>
       <c r="G3" t="n">
-        <v>13465</v>
+        <v>13492</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O3" t="n">
         <v>135</v>
@@ -658,10 +658,10 @@
         <v>135</v>
       </c>
       <c r="Q3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R3" t="n">
-        <v>12522</v>
+        <v>12548</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:10</t>
+          <t>2026-09-21 20:41:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:13</t>
+          <t>2026-09-21 20:41:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85248</v>
+        <v>2.85209</v>
       </c>
       <c r="G5" t="n">
-        <v>3159</v>
+        <v>3164</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="O5" t="n">
         <v>158</v>
@@ -802,10 +802,10 @@
         <v>95</v>
       </c>
       <c r="Q5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R5" t="n">
-        <v>1295</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:15</t>
+          <t>2026-09-21 20:41:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:17</t>
+          <t>2026-09-21 20:41:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9839</v>
+        <v>3.98469</v>
       </c>
       <c r="G7" t="n">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>417</v>
       </c>
       <c r="R7" t="n">
-        <v>2386</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:19</t>
+          <t>2026-09-21 20:41:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:22</t>
+          <t>2026-09-21 20:41:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:24</t>
+          <t>2026-09-21 20:41:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:26</t>
+          <t>2026-09-21 20:41:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:28</t>
+          <t>2026-09-21 20:42:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70803</v>
+        <v>4.70983</v>
       </c>
       <c r="G12" t="n">
-        <v>3110</v>
+        <v>3112</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>September 21, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>156</v>
       </c>
       <c r="R12" t="n">
-        <v>2706</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:31</t>
+          <t>2026-09-21 20:42:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:33</t>
+          <t>2026-09-21 20:42:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:35</t>
+          <t>2026-09-21 20:42:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:37</t>
+          <t>2026-09-21 20:42:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74118</v>
+        <v>4.74129</v>
       </c>
       <c r="G16" t="n">
-        <v>32626</v>
+        <v>32639</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="O16" t="n">
         <v>326</v>
@@ -1594,10 +1594,10 @@
         <v>653</v>
       </c>
       <c r="Q16" t="n">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="R16" t="n">
-        <v>29037</v>
+        <v>29049</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:37</t>
+          <t>2026-09-22 19:56:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,29 +600,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:40</t>
+          <t>2026-09-22 19:56:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>com.bankaletihad.iphone.etihadmobilepro</t>
+          <t>com.arabbank.arabimobilev2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bank al Etihad | بنك الإتحاد</t>
+          <t>Arabi-Mobile</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bank al Etihad | بنك الإتحاد</t>
+          <t>Arabi-Mobile</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81263</v>
+        <v>3.87572</v>
       </c>
       <c r="G3" t="n">
-        <v>13492</v>
+        <v>4860</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,33 +635,33 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.2</t>
+          <t>2.22.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>December 28, 2015</t>
+          <t>August 05, 2018</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>September 17, 2026</t>
+          <t>September 08, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>405</v>
+        <v>972</v>
       </c>
       <c r="O3" t="n">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="P3" t="n">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="Q3" t="n">
-        <v>270</v>
+        <v>389</v>
       </c>
       <c r="R3" t="n">
-        <v>12548</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="4">
@@ -672,29 +672,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:42</t>
+          <t>2026-09-22 19:56:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>com.arabbank.arabimobilev2</t>
+          <t>com.mobilebanking.jib</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Arabi-Mobile</t>
+          <t>Jordan Islamic Bank</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arabi-Mobile</t>
+          <t>Jordan Islamic Bank</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87631</v>
+        <v>2.85304</v>
       </c>
       <c r="G4" t="n">
-        <v>4859</v>
+        <v>3171</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -707,33 +707,33 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.2</t>
+          <t>10.6.8</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>August 05, 2018</t>
+          <t>January 28, 2020</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>September 08, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>972</v>
+        <v>1490</v>
       </c>
       <c r="O4" t="n">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
-        <v>243</v>
+        <v>95</v>
       </c>
       <c r="Q4" t="n">
-        <v>389</v>
+        <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>3013</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="5">
@@ -744,29 +744,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:44</t>
+          <t>2026-09-22 19:56:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>com.mobilebanking.jib</t>
+          <t>com.icsfs.safwamobile</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jordan Islamic Bank</t>
+          <t>Safwa Islamic Bank</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan Islamic Bank</t>
+          <t>Safwa Islamic Bank</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85209</v>
+        <v>3.31183</v>
       </c>
       <c r="G5" t="n">
-        <v>3164</v>
+        <v>186</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,12 +779,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.6.8</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>January 28, 2020</t>
+          <t>May 18, 2017</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1487</v>
+        <v>61</v>
       </c>
       <c r="O5" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>1297</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -816,29 +816,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:46</t>
+          <t>2026-09-22 19:56:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>com.icsfs.safwamobile</t>
+          <t>com.jo.hbtf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Safwa Islamic Bank</t>
+          <t>Iskan Mobile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Safwa Islamic Bank</t>
+          <t>Iskan Mobile</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3027</v>
+        <v>3.98417</v>
       </c>
       <c r="G6" t="n">
-        <v>185</v>
+        <v>3791</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -851,33 +851,33 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>May 18, 2017</t>
+          <t>June 11, 2020</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>September 16, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>61</v>
+        <v>644</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>417</v>
       </c>
       <c r="R6" t="n">
-        <v>87</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="7">
@@ -888,29 +888,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:49</t>
+          <t>2026-09-22 19:56:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>com.jo.hbtf</t>
+          <t>com.capital.cbt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Iskan Mobile</t>
+          <t>Capital Bank Mobile – Jordan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Iskan Mobile</t>
+          <t>Capital Bank Mobile – Jordan</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98469</v>
+        <v>4.74191</v>
       </c>
       <c r="G7" t="n">
-        <v>3789</v>
+        <v>13627</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,33 +923,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>June 11, 2020</t>
+          <t>June 23, 2022</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>September 16, 2026</t>
+          <t>September 01, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>644</v>
+        <v>545</v>
       </c>
       <c r="O7" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="P7" t="n">
-        <v>189</v>
+        <v>273</v>
       </c>
       <c r="Q7" t="n">
-        <v>417</v>
+        <v>545</v>
       </c>
       <c r="R7" t="n">
-        <v>2387</v>
+        <v>12128</v>
       </c>
     </row>
     <row r="8">
@@ -960,29 +960,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:51</t>
+          <t>2026-09-22 19:56:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>com.capital.cbt</t>
+          <t>com.ubanquity.ahli</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Capital Bank Mobile – Jordan</t>
+          <t>Ahli Mobile: Banking Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Capital Bank Mobile – Jordan</t>
+          <t>Ahli Mobile: Banking Services</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74191</v>
+        <v>4.61388</v>
       </c>
       <c r="G8" t="n">
-        <v>13627</v>
+        <v>720</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -995,33 +995,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>June 23, 2022</t>
+          <t>April 01, 2012</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>September 01, 2026</t>
+          <t>August 16, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>545</v>
+        <v>50</v>
       </c>
       <c r="O8" t="n">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>273</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>22</v>
       </c>
       <c r="R8" t="n">
-        <v>12128</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:53</t>
+          <t>2026-09-22 19:56:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>com.ubanquity.ahli</t>
+          <t>com.bankofjordan.rmobileapp</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ahli Mobile: Banking Services</t>
+          <t>BOJ Mobile - بنك الأردن</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ahli Mobile: Banking Services</t>
+          <t>BOJ Mobile - بنك الأردن</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61388</v>
+        <v>3.88534</v>
       </c>
       <c r="G9" t="n">
-        <v>720</v>
+        <v>1064</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1067,33 +1067,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>2.1.29</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>April 01, 2012</t>
+          <t>August 23, 2018</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>August 16, 2026</t>
+          <t>September 02, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="R9" t="n">
-        <v>626</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10">
@@ -1104,29 +1104,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:55</t>
+          <t>2026-09-22 19:56:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>com.bankofjordan.rmobileapp</t>
+          <t>A2A.CABBank</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOJ Mobile - بنك الأردن</t>
+          <t>CAB Mobile Banking</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BOJ Mobile - بنك الأردن</t>
+          <t>CAB Mobile Banking</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.88429</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1063</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.29</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>August 23, 2018</t>
+          <t>November 27, 2014</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>691</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1176,29 +1176,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:57</t>
+          <t>2026-09-22 19:56:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A2A.CABBank</t>
+          <t>com.icsfs.ajibmobile</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CAB Mobile Banking</t>
+          <t>AJIB Mobile</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAB Mobile Banking</t>
+          <t>AJIB Mobile</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.59184</v>
+        <v>4.71075</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>3115</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,33 +1211,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>November 27, 2014</t>
+          <t>March 20, 2017</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>September 02, 2026</t>
+          <t>September 21, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="12">
@@ -1248,29 +1248,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 20:42:00</t>
+          <t>2026-09-22 19:56:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>com.icsfs.ajibmobile</t>
+          <t>com.mob.jkb</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AJIB Mobile</t>
+          <t>JKBMobile</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AJIB Mobile</t>
+          <t>JKBMobile</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70983</v>
+        <v>4.00345</v>
       </c>
       <c r="G12" t="n">
-        <v>3112</v>
+        <v>579</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,33 +1283,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.8.2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>March 20, 2017</t>
+          <t>July 21, 2022</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>September 21, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="P12" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="R12" t="n">
-        <v>2739</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 20:42:02</t>
+          <t>2026-09-22 19:56:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>com.mob.jkb</t>
+          <t>com.icsfs.alrajhi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JKBMobile</t>
+          <t>AlRajhi Mobile JO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JKBMobile</t>
+          <t>AlRajhi Mobile JO</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00345</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>579</v>
+        <v>244</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1355,33 +1355,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.8.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>July 21, 2022</t>
+          <t>May 11, 2024</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>September 14, 2026</t>
+          <t>September 20, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="O13" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>400</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14">
@@ -1392,29 +1392,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 20:42:04</t>
+          <t>2026-09-22 19:56:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>com.icsfs.alrajhi</t>
+          <t>com.blombank.eblom.eBLOM-Mobile-Jordan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AlRajhi Mobile JO</t>
+          <t>eBLOM Mobile-Jordan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AlRajhi Mobile JO</t>
+          <t>eBLOM Mobile-Jordan</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>1.83333</v>
       </c>
       <c r="G14" t="n">
-        <v>244</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1427,33 +1427,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>May 11, 2024</t>
+          <t>May 15, 2017</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>September 20, 2026</t>
+          <t>February 27, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 20:42:06</t>
+          <t>2026-09-22 19:56:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>com.blombank.eblom.eBLOM-Mobile-Jordan</t>
+          <t>com.iiab.mobilebanking</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>eBLOM Mobile-Jordan</t>
+          <t>Arabi Islami Mobile</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>eBLOM Mobile-Jordan</t>
+          <t>Arabi Islami Mobile</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.83333</v>
+        <v>4.74078</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>32652</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1499,105 +1499,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>May 15, 2017</t>
+          <t>November 17, 2021</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>February 27, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>1306</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>653</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1306</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>App Store</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-21 20:42:09</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>com.iiab.mobilebanking</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Arabi Islami Mobile</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Arabi Islami Mobile</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>4.74129</v>
-      </c>
-      <c r="G16" t="n">
-        <v>32639</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>3.1.7</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>November 17, 2021</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>September 14, 2026</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>1306</v>
-      </c>
-      <c r="O16" t="n">
-        <v>326</v>
-      </c>
-      <c r="P16" t="n">
-        <v>653</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1306</v>
-      </c>
-      <c r="R16" t="n">
-        <v>29049</v>
+        <v>29060</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:27</t>
+          <t>2026-09-23 19:55:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:30</t>
+          <t>2026-09-23 19:55:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.87572</v>
+        <v>3.87595</v>
       </c>
       <c r="G3" t="n">
-        <v>4860</v>
+        <v>4861</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>389</v>
       </c>
       <c r="R3" t="n">
-        <v>3013</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:32</t>
+          <t>2026-09-23 19:55:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.85304</v>
+        <v>2.85274</v>
       </c>
       <c r="G4" t="n">
-        <v>3171</v>
+        <v>3178</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="O4" t="n">
         <v>159</v>
@@ -733,7 +733,7 @@
         <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:34</t>
+          <t>2026-09-23 19:55:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:37</t>
+          <t>2026-09-23 19:55:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.98417</v>
+        <v>3.98234</v>
       </c>
       <c r="G6" t="n">
-        <v>3791</v>
+        <v>3794</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O6" t="n">
         <v>152</v>
@@ -877,7 +877,7 @@
         <v>417</v>
       </c>
       <c r="R6" t="n">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:39</t>
+          <t>2026-09-23 19:55:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:42</t>
+          <t>2026-09-23 19:55:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:44</t>
+          <t>2026-09-23 19:55:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:46</t>
+          <t>2026-09-23 19:55:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:49</t>
+          <t>2026-09-23 19:55:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.71075</v>
+        <v>4.71244</v>
       </c>
       <c r="G11" t="n">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>156</v>
       </c>
       <c r="R11" t="n">
-        <v>2741</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:51</t>
+          <t>2026-09-23 19:55:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:54</t>
+          <t>2026-09-23 19:55:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3.4898</v>
       </c>
       <c r="G13" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1381,7 +1381,7 @@
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:56</t>
+          <t>2026-09-23 19:55:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:58</t>
+          <t>2026-09-23 19:55:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.74078</v>
+        <v>4.74085</v>
       </c>
       <c r="G15" t="n">
-        <v>32652</v>
+        <v>32666</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="O15" t="n">
         <v>327</v>
@@ -1522,10 +1522,10 @@
         <v>653</v>
       </c>
       <c r="Q15" t="n">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="R15" t="n">
-        <v>29060</v>
+        <v>29073</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:06</t>
+          <t>2026-09-24 20:13:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:09</t>
+          <t>2026-09-24 20:13:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:11</t>
+          <t>2026-09-24 20:13:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.85274</v>
+        <v>2.84937</v>
       </c>
       <c r="G4" t="n">
-        <v>3178</v>
+        <v>3180</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1494</v>
+        <v>1526</v>
       </c>
       <c r="O4" t="n">
         <v>159</v>
@@ -733,7 +733,7 @@
         <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:13</t>
+          <t>2026-09-24 20:13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:16</t>
+          <t>2026-09-24 20:13:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.98234</v>
+        <v>3.98288</v>
       </c>
       <c r="G6" t="n">
-        <v>3794</v>
+        <v>3796</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -874,10 +874,10 @@
         <v>190</v>
       </c>
       <c r="Q6" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R6" t="n">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:18</t>
+          <t>2026-09-24 20:13:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:21</t>
+          <t>2026-09-24 20:13:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:23</t>
+          <t>2026-09-24 20:13:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:26</t>
+          <t>2026-09-24 20:13:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:28</t>
+          <t>2026-09-24 20:13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.71244</v>
+        <v>4.71346</v>
       </c>
       <c r="G11" t="n">
-        <v>3116</v>
+        <v>3120</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>156</v>
       </c>
       <c r="R11" t="n">
-        <v>2742</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:31</t>
+          <t>2026-09-24 20:13:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:33</t>
+          <t>2026-09-24 20:13:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4898</v>
+        <v>3.47967</v>
       </c>
       <c r="G13" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1381,7 +1381,7 @@
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:35</t>
+          <t>2026-09-24 20:13:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:38</t>
+          <t>2026-09-24 20:13:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.74085</v>
+        <v>4.74052</v>
       </c>
       <c r="G15" t="n">
-        <v>32666</v>
+        <v>32689</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="O15" t="n">
         <v>327</v>
       </c>
       <c r="P15" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q15" t="n">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="R15" t="n">
-        <v>29073</v>
+        <v>29093</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:21</t>
+          <t>2026-09-25 20:10:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:25</t>
+          <t>2026-09-25 20:10:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:27</t>
+          <t>2026-09-25 20:10:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.84937</v>
+        <v>2.85127</v>
       </c>
       <c r="G4" t="n">
-        <v>3180</v>
+        <v>3187</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="O4" t="n">
         <v>159</v>
       </c>
       <c r="P4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q4" t="n">
         <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:30</t>
+          <t>2026-09-25 20:10:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:32</t>
+          <t>2026-09-25 20:10:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.98288</v>
+        <v>3.98419</v>
       </c>
       <c r="G6" t="n">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         <v>190</v>
       </c>
       <c r="Q6" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R6" t="n">
         <v>2391</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:35</t>
+          <t>2026-09-25 20:10:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:37</t>
+          <t>2026-09-25 20:10:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.61388</v>
+        <v>4.60888</v>
       </c>
       <c r="G8" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="R8" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:40</t>
+          <t>2026-09-25 20:10:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:42</t>
+          <t>2026-09-25 20:10:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:45</t>
+          <t>2026-09-25 20:10:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.71346</v>
+        <v>4.71502</v>
       </c>
       <c r="G11" t="n">
-        <v>3120</v>
+        <v>3123</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>156</v>
       </c>
       <c r="R11" t="n">
-        <v>2746</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:47</t>
+          <t>2026-09-25 20:11:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.00345</v>
+        <v>3.99828</v>
       </c>
       <c r="G12" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:50</t>
+          <t>2026-09-25 20:11:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.47967</v>
+        <v>3.47177</v>
       </c>
       <c r="G13" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:52</t>
+          <t>2026-09-25 20:11:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:55</t>
+          <t>2026-09-25 20:11:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.74052</v>
+        <v>4.74015</v>
       </c>
       <c r="G15" t="n">
-        <v>32689</v>
+        <v>32727</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="O15" t="n">
         <v>327</v>
       </c>
       <c r="P15" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Q15" t="n">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="R15" t="n">
-        <v>29093</v>
+        <v>29127</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:39</t>
+          <t>2026-09-26 19:29:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:42</t>
+          <t>2026-09-26 19:29:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:44</t>
+          <t>2026-09-26 19:30:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.85127</v>
+        <v>2.85069</v>
       </c>
       <c r="G4" t="n">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>96</v>
       </c>
       <c r="Q4" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R4" t="n">
         <v>1307</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:46</t>
+          <t>2026-09-26 19:30:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:48</t>
+          <t>2026-09-26 19:30:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.98419</v>
+        <v>3.98394</v>
       </c>
       <c r="G6" t="n">
-        <v>3795</v>
+        <v>3798</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O6" t="n">
         <v>152</v>
@@ -874,10 +874,10 @@
         <v>190</v>
       </c>
       <c r="Q6" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R6" t="n">
-        <v>2391</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:50</t>
+          <t>2026-09-26 19:30:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:53</t>
+          <t>2026-09-26 19:30:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:55</t>
+          <t>2026-09-26 19:30:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:57</t>
+          <t>2026-09-26 19:30:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:59</t>
+          <t>2026-09-26 19:30:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.71502</v>
+        <v>4.71534</v>
       </c>
       <c r="G11" t="n">
         <v>3123</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-25 20:11:01</t>
+          <t>2026-09-26 19:30:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-25 20:11:04</t>
+          <t>2026-09-26 19:30:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-25 20:11:06</t>
+          <t>2026-09-26 19:30:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-25 20:11:08</t>
+          <t>2026-09-26 19:30:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.74015</v>
+        <v>4.74047</v>
       </c>
       <c r="G15" t="n">
-        <v>32727</v>
+        <v>32732</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>1309</v>
       </c>
       <c r="R15" t="n">
-        <v>29127</v>
+        <v>29131</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:56</t>
+          <t>2026-09-27 19:55:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:58</t>
+          <t>2026-09-27 19:55:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:00</t>
+          <t>2026-09-27 19:55:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.85069</v>
+        <v>2.8502</v>
       </c>
       <c r="G4" t="n">
-        <v>3188</v>
+        <v>3191</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P4" t="n">
         <v>96</v>
@@ -733,7 +733,7 @@
         <v>128</v>
       </c>
       <c r="R4" t="n">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:03</t>
+          <t>2026-09-27 19:55:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:05</t>
+          <t>2026-09-27 19:55:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.98394</v>
+        <v>3.98472</v>
       </c>
       <c r="G6" t="n">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="O6" t="n">
         <v>152</v>
@@ -877,7 +877,7 @@
         <v>418</v>
       </c>
       <c r="R6" t="n">
-        <v>2393</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:07</t>
+          <t>2026-09-27 19:55:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.74191</v>
+        <v>4.74189</v>
       </c>
       <c r="G7" t="n">
-        <v>13627</v>
+        <v>13626</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>545</v>
       </c>
       <c r="R7" t="n">
-        <v>12128</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:09</t>
+          <t>2026-09-27 19:55:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:11</t>
+          <t>2026-09-27 19:55:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:14</t>
+          <t>2026-09-27 19:55:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>2.60784</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:16</t>
+          <t>2026-09-27 19:55:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.71534</v>
+        <v>4.71359</v>
       </c>
       <c r="G11" t="n">
-        <v>3123</v>
+        <v>3125</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>156</v>
       </c>
       <c r="R11" t="n">
-        <v>2748</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:18</t>
+          <t>2026-09-27 19:55:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:21</t>
+          <t>2026-09-27 19:55:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:23</t>
+          <t>2026-09-27 19:55:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:25</t>
+          <t>2026-09-27 19:55:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.74047</v>
+        <v>4.74095</v>
       </c>
       <c r="G15" t="n">
-        <v>32732</v>
+        <v>32746</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="O15" t="n">
         <v>327</v>
@@ -1522,10 +1522,10 @@
         <v>655</v>
       </c>
       <c r="Q15" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="R15" t="n">
-        <v>29131</v>
+        <v>29144</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:00</t>
+          <t>2026-09-28 22:19:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.61628</v>
+        <v>4.6185</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,29 +600,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:03</t>
+          <t>2026-09-28 22:19:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>com.arabbank.arabimobilev2</t>
+          <t>com.bankaletihad.iphone.etihadmobilepro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Arabi-Mobile</t>
+          <t>Bank al Etihad | بنك الإتحاد</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arabi-Mobile</t>
+          <t>Bank al Etihad | بنك الإتحاد</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.87595</v>
+        <v>4.81306</v>
       </c>
       <c r="G3" t="n">
-        <v>4861</v>
+        <v>13518</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,33 +635,33 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.22.2</t>
+          <t>4.46.3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>August 05, 2018</t>
+          <t>December 28, 2015</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>September 08, 2026</t>
+          <t>September 25, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>972</v>
+        <v>406</v>
       </c>
       <c r="O3" t="n">
-        <v>243</v>
+        <v>135</v>
       </c>
       <c r="P3" t="n">
-        <v>243</v>
+        <v>135</v>
       </c>
       <c r="Q3" t="n">
-        <v>389</v>
+        <v>270</v>
       </c>
       <c r="R3" t="n">
-        <v>3014</v>
+        <v>12572</v>
       </c>
     </row>
     <row r="4">
@@ -672,29 +672,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:05</t>
+          <t>2026-09-28 22:19:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>com.mobilebanking.jib</t>
+          <t>com.arabbank.arabimobilev2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jordan Islamic Bank</t>
+          <t>Arabi-Mobile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan Islamic Bank</t>
+          <t>Arabi-Mobile</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8502</v>
+        <v>3.87595</v>
       </c>
       <c r="G4" t="n">
-        <v>3191</v>
+        <v>4861</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -707,33 +707,33 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10.6.8</t>
+          <t>2.22.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>January 28, 2020</t>
+          <t>August 05, 2018</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>September 08, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1532</v>
+        <v>972</v>
       </c>
       <c r="O4" t="n">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="P4" t="n">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="Q4" t="n">
-        <v>128</v>
+        <v>389</v>
       </c>
       <c r="R4" t="n">
-        <v>1308</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="5">
@@ -744,29 +744,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:07</t>
+          <t>2026-09-28 22:19:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>com.icsfs.safwamobile</t>
+          <t>com.mobilebanking.jib</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Safwa Islamic Bank</t>
+          <t>Jordan Islamic Bank</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Safwa Islamic Bank</t>
+          <t>Jordan Islamic Bank</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.31183</v>
+        <v>2.85088</v>
       </c>
       <c r="G5" t="n">
-        <v>186</v>
+        <v>3192</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,12 +779,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>10.6.8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>May 18, 2017</t>
+          <t>January 28, 2020</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>61</v>
+        <v>1532</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="R5" t="n">
-        <v>87</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="6">
@@ -816,29 +816,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:09</t>
+          <t>2026-09-28 22:19:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>com.jo.hbtf</t>
+          <t>com.icsfs.safwamobile</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Iskan Mobile</t>
+          <t>Safwa Islamic Bank</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iskan Mobile</t>
+          <t>Safwa Islamic Bank</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.98472</v>
+        <v>3.31183</v>
       </c>
       <c r="G6" t="n">
-        <v>3797</v>
+        <v>186</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -851,33 +851,33 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>June 11, 2020</t>
+          <t>May 18, 2017</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>September 16, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>645</v>
+        <v>61</v>
       </c>
       <c r="O6" t="n">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>418</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>2392</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -888,29 +888,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:12</t>
+          <t>2026-09-28 22:19:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>com.capital.cbt</t>
+          <t>com.jo.hbtf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Capital Bank Mobile – Jordan</t>
+          <t>Iskan Mobile</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Capital Bank Mobile – Jordan</t>
+          <t>Iskan Mobile</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.74189</v>
+        <v>3.98394</v>
       </c>
       <c r="G7" t="n">
-        <v>13626</v>
+        <v>3799</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,33 +923,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>June 23, 2022</t>
+          <t>June 11, 2020</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>September 01, 2026</t>
+          <t>September 16, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>545</v>
+        <v>646</v>
       </c>
       <c r="O7" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="P7" t="n">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="Q7" t="n">
-        <v>545</v>
+        <v>418</v>
       </c>
       <c r="R7" t="n">
-        <v>12127</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="8">
@@ -960,29 +960,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:14</t>
+          <t>2026-09-28 22:19:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>com.ubanquity.ahli</t>
+          <t>com.capital.cbt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ahli Mobile: Banking Services</t>
+          <t>Capital Bank Mobile – Jordan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ahli Mobile: Banking Services</t>
+          <t>Capital Bank Mobile – Jordan</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.60888</v>
+        <v>4.74189</v>
       </c>
       <c r="G8" t="n">
-        <v>721</v>
+        <v>13626</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -995,33 +995,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>April 01, 2012</t>
+          <t>June 23, 2022</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>August 16, 2026</t>
+          <t>September 01, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>545</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>627</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="9">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:16</t>
+          <t>2026-09-28 22:19:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>com.bankofjordan.rmobileapp</t>
+          <t>com.ubanquity.ahli</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOJ Mobile - بنك الأردن</t>
+          <t>Ahli Mobile: Banking Services</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BOJ Mobile - بنك الأردن</t>
+          <t>Ahli Mobile: Banking Services</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.88534</v>
+        <v>4.60888</v>
       </c>
       <c r="G9" t="n">
-        <v>1064</v>
+        <v>721</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1067,33 +1067,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.1.29</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>August 23, 2018</t>
+          <t>April 01, 2012</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>September 02, 2026</t>
+          <t>August 16, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>234</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>692</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10">
@@ -1104,29 +1104,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:19</t>
+          <t>2026-09-28 22:19:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A2A.CABBank</t>
+          <t>com.bankofjordan.rmobileapp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CAB Mobile Banking</t>
+          <t>BOJ Mobile - بنك الأردن</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAB Mobile Banking</t>
+          <t>BOJ Mobile - بنك الأردن</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.60784</v>
+        <v>3.88534</v>
       </c>
       <c r="G10" t="n">
-        <v>51</v>
+        <v>1064</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>2.1.29</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>November 27, 2014</t>
+          <t>August 23, 2018</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>18</v>
+        <v>692</v>
       </c>
     </row>
     <row r="11">
@@ -1176,29 +1176,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:21</t>
+          <t>2026-09-28 22:19:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>com.icsfs.ajibmobile</t>
+          <t>A2A.CABBank</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AJIB Mobile</t>
+          <t>CAB Mobile Banking</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AJIB Mobile</t>
+          <t>CAB Mobile Banking</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.71359</v>
+        <v>2.60784</v>
       </c>
       <c r="G11" t="n">
-        <v>3125</v>
+        <v>51</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,33 +1211,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>March 20, 2017</t>
+          <t>November 27, 2014</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>September 21, 2026</t>
+          <t>September 02, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>2750</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -1248,29 +1248,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:23</t>
+          <t>2026-09-28 22:19:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>com.mob.jkb</t>
+          <t>com.icsfs.ajibmobile</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JKBMobile</t>
+          <t>AJIB Mobile</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JKBMobile</t>
+          <t>AJIB Mobile</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.99828</v>
+        <v>4.71378</v>
       </c>
       <c r="G12" t="n">
-        <v>580</v>
+        <v>3127</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,33 +1283,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.8.2</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>July 21, 2022</t>
+          <t>March 20, 2017</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>September 14, 2026</t>
+          <t>September 21, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="O12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="R12" t="n">
-        <v>400</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="13">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:26</t>
+          <t>2026-09-28 22:19:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>com.icsfs.alrajhi</t>
+          <t>com.mob.jkb</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AlRajhi Mobile JO</t>
+          <t>JKBMobile</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AlRajhi Mobile JO</t>
+          <t>JKBMobile</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.47177</v>
+        <v>3.99828</v>
       </c>
       <c r="G13" t="n">
-        <v>248</v>
+        <v>580</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1355,33 +1355,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.8.2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>May 11, 2024</t>
+          <t>July 21, 2022</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>September 20, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>146</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
@@ -1392,29 +1392,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:28</t>
+          <t>2026-09-28 22:19:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>com.blombank.eblom.eBLOM-Mobile-Jordan</t>
+          <t>com.icsfs.alrajhi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>eBLOM Mobile-Jordan</t>
+          <t>AlRajhi Mobile JO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>eBLOM Mobile-Jordan</t>
+          <t>AlRajhi Mobile JO</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.83333</v>
+        <v>3.47177</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1427,33 +1427,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>May 15, 2017</t>
+          <t>May 11, 2024</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>February 27, 2026</t>
+          <t>September 20, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -1464,68 +1464,140 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-27 19:55:30</t>
+          <t>2026-09-28 22:19:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>com.blombank.eblom.eBLOM-Mobile-Jordan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>eBLOM Mobile-Jordan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>eBLOM Mobile-Jordan</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.83333</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>May 15, 2017</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>February 27, 2026</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>App Store</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:48</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>com.iiab.mobilebanking</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Arabi Islami Mobile</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Arabi Islami Mobile</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>4.74095</v>
-      </c>
-      <c r="G15" t="n">
-        <v>32746</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="F16" t="n">
+        <v>4.74117</v>
+      </c>
+      <c r="G16" t="n">
+        <v>32759</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>3.1.7</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>November 17, 2021</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>September 14, 2026</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>1310</v>
       </c>
-      <c r="O15" t="n">
-        <v>327</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="O16" t="n">
+        <v>328</v>
+      </c>
+      <c r="P16" t="n">
         <v>655</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>1310</v>
       </c>
-      <c r="R15" t="n">
-        <v>29144</v>
+      <c r="R16" t="n">
+        <v>29156</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:17</t>
+          <t>2026-09-29 21:06:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.6185</v>
+        <v>4.61628</v>
       </c>
       <c r="G2" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:19</t>
+          <t>2026-09-29 21:06:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81306</v>
+        <v>4.81304</v>
       </c>
       <c r="G3" t="n">
-        <v>13518</v>
+        <v>13517</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>270</v>
       </c>
       <c r="R3" t="n">
-        <v>12572</v>
+        <v>12571</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:21</t>
+          <t>2026-09-29 21:06:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:23</t>
+          <t>2026-09-29 21:07:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85088</v>
+        <v>2.85048</v>
       </c>
       <c r="G5" t="n">
-        <v>3192</v>
+        <v>3197</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="O5" t="n">
         <v>160</v>
@@ -805,7 +805,7 @@
         <v>128</v>
       </c>
       <c r="R5" t="n">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:26</t>
+          <t>2026-09-29 21:07:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:28</t>
+          <t>2026-09-29 21:07:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98394</v>
+        <v>3.98368</v>
       </c>
       <c r="G7" t="n">
         <v>3799</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:30</t>
+          <t>2026-09-29 21:07:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:33</t>
+          <t>2026-09-29 21:07:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:35</t>
+          <t>2026-09-29 21:07:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:37</t>
+          <t>2026-09-29 21:07:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:39</t>
+          <t>2026-09-29 21:07:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71378</v>
+        <v>4.71397</v>
       </c>
       <c r="G12" t="n">
-        <v>3127</v>
+        <v>3129</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>156</v>
       </c>
       <c r="R12" t="n">
-        <v>2752</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:42</t>
+          <t>2026-09-29 21:07:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:44</t>
+          <t>2026-09-29 21:07:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:46</t>
+          <t>2026-09-29 21:07:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:48</t>
+          <t>2026-09-29 21:07:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74117</v>
+        <v>4.74089</v>
       </c>
       <c r="G16" t="n">
-        <v>32759</v>
+        <v>32778</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
       </c>
       <c r="P16" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Q16" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="R16" t="n">
-        <v>29156</v>
+        <v>29172</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:53</t>
+          <t>2026-09-30 21:05:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:56</t>
+          <t>2026-09-30 21:05:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81304</v>
+        <v>4.81236</v>
       </c>
       <c r="G3" t="n">
-        <v>13517</v>
+        <v>13531</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>135</v>
       </c>
       <c r="Q3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R3" t="n">
-        <v>12571</v>
+        <v>12584</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:58</t>
+          <t>2026-09-30 21:05:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:01</t>
+          <t>2026-09-30 21:05:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:04</t>
+          <t>2026-09-30 21:05:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:06</t>
+          <t>2026-09-30 21:05:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:09</t>
+          <t>2026-09-30 21:05:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74189</v>
+        <v>4.74191</v>
       </c>
       <c r="G8" t="n">
-        <v>13626</v>
+        <v>13627</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12127</v>
+        <v>12128</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:12</t>
+          <t>2026-09-30 21:05:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60888</v>
+        <v>4.60832</v>
       </c>
       <c r="G9" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:14</t>
+          <t>2026-09-30 21:05:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:17</t>
+          <t>2026-09-30 21:05:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:19</t>
+          <t>2026-09-30 21:05:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71397</v>
+        <v>4.71021</v>
       </c>
       <c r="G12" t="n">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:21</t>
+          <t>2026-09-30 21:05:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:24</t>
+          <t>2026-09-30 21:05:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:26</t>
+          <t>2026-09-30 21:06:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 21:07:28</t>
+          <t>2026-09-30 21:06:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74089</v>
+        <v>4.74096</v>
       </c>
       <c r="G16" t="n">
-        <v>32778</v>
+        <v>32787</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1311</v>
       </c>
       <c r="R16" t="n">
-        <v>29172</v>
+        <v>29180</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:31</t>
+          <t>2026-10-01 21:26:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:33</t>
+          <t>2026-10-01 21:27:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81236</v>
+        <v>4.81234</v>
       </c>
       <c r="G3" t="n">
-        <v>13531</v>
+        <v>13551</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q3" t="n">
         <v>271</v>
       </c>
       <c r="R3" t="n">
-        <v>12584</v>
+        <v>12602</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:35</t>
+          <t>2026-10-01 21:27:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:37</t>
+          <t>2026-10-01 21:27:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85048</v>
+        <v>2.85005</v>
       </c>
       <c r="G5" t="n">
-        <v>3197</v>
+        <v>3201</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="O5" t="n">
         <v>160</v>
@@ -805,7 +805,7 @@
         <v>128</v>
       </c>
       <c r="R5" t="n">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:40</t>
+          <t>2026-10-01 21:27:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:42</t>
+          <t>2026-10-01 21:27:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98368</v>
+        <v>3.98396</v>
       </c>
       <c r="G7" t="n">
-        <v>3799</v>
+        <v>3802</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>418</v>
       </c>
       <c r="R7" t="n">
-        <v>2393</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:44</t>
+          <t>2026-10-01 21:27:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:46</t>
+          <t>2026-10-01 21:27:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60832</v>
+        <v>4.60472</v>
       </c>
       <c r="G9" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:49</t>
+          <t>2026-10-01 21:27:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:51</t>
+          <t>2026-10-01 21:27:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:54</t>
+          <t>2026-10-01 21:27:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71021</v>
+        <v>4.71049</v>
       </c>
       <c r="G12" t="n">
-        <v>3130</v>
+        <v>3133</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R12" t="n">
-        <v>2754</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:56</t>
+          <t>2026-10-01 21:27:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:58</t>
+          <t>2026-10-01 21:27:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-30 21:06:00</t>
+          <t>2026-10-01 21:27:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-30 21:06:02</t>
+          <t>2026-10-01 21:27:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74096</v>
+        <v>4.74035</v>
       </c>
       <c r="G16" t="n">
-        <v>32787</v>
+        <v>32809</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
@@ -1594,10 +1594,10 @@
         <v>656</v>
       </c>
       <c r="Q16" t="n">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="R16" t="n">
-        <v>29180</v>
+        <v>29200</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:58</t>
+          <t>2026-10-02 21:04:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:00</t>
+          <t>2026-10-02 21:05:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:03</t>
+          <t>2026-10-02 21:05:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:05</t>
+          <t>2026-10-02 21:05:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85005</v>
+        <v>2.84956</v>
       </c>
       <c r="G5" t="n">
-        <v>3201</v>
+        <v>3204</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="O5" t="n">
         <v>160</v>
@@ -805,7 +805,7 @@
         <v>128</v>
       </c>
       <c r="R5" t="n">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:07</t>
+          <t>2026-10-02 21:05:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:10</t>
+          <t>2026-10-02 21:05:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:12</t>
+          <t>2026-10-02 21:05:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:14</t>
+          <t>2026-10-02 21:05:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:17</t>
+          <t>2026-10-02 21:05:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.88534</v>
+        <v>3.88638</v>
       </c>
       <c r="G10" t="n">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:19</t>
+          <t>2026-10-02 21:05:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:21</t>
+          <t>2026-10-02 21:05:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71049</v>
+        <v>4.71078</v>
       </c>
       <c r="G12" t="n">
-        <v>3133</v>
+        <v>3136</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>157</v>
       </c>
       <c r="R12" t="n">
-        <v>2757</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:24</t>
+          <t>2026-10-02 21:05:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:26</t>
+          <t>2026-10-02 21:05:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:29</t>
+          <t>2026-10-02 21:05:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-01 21:27:32</t>
+          <t>2026-10-02 21:05:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74035</v>
+        <v>4.74003</v>
       </c>
       <c r="G16" t="n">
-        <v>32809</v>
+        <v>32832</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
       </c>
       <c r="P16" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Q16" t="n">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="R16" t="n">
-        <v>29200</v>
+        <v>29220</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:57</t>
+          <t>2026-10-03 19:34:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:00</t>
+          <t>2026-10-03 19:34:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81234</v>
+        <v>4.81155</v>
       </c>
       <c r="G3" t="n">
-        <v>13551</v>
+        <v>13579</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>136</v>
       </c>
       <c r="Q3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="R3" t="n">
-        <v>12602</v>
+        <v>12628</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:02</t>
+          <t>2026-10-03 19:34:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87595</v>
+        <v>3.87446</v>
       </c>
       <c r="G4" t="n">
-        <v>4861</v>
+        <v>4867</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="O4" t="n">
         <v>243</v>
@@ -733,7 +733,7 @@
         <v>389</v>
       </c>
       <c r="R4" t="n">
-        <v>3014</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:05</t>
+          <t>2026-10-03 19:34:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84956</v>
+        <v>2.85069</v>
       </c>
       <c r="G5" t="n">
-        <v>3204</v>
+        <v>3208</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="O5" t="n">
         <v>160</v>
@@ -805,7 +805,7 @@
         <v>128</v>
       </c>
       <c r="R5" t="n">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:07</t>
+          <t>2026-10-03 19:34:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:10</t>
+          <t>2026-10-03 19:34:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98396</v>
+        <v>3.98422</v>
       </c>
       <c r="G7" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O7" t="n">
         <v>152</v>
@@ -949,7 +949,7 @@
         <v>418</v>
       </c>
       <c r="R7" t="n">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:12</t>
+          <t>2026-10-03 19:34:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:15</t>
+          <t>2026-10-03 19:34:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:17</t>
+          <t>2026-10-03 19:34:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:19</t>
+          <t>2026-10-03 19:34:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:22</t>
+          <t>2026-10-03 19:34:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71078</v>
+        <v>4.71046</v>
       </c>
       <c r="G12" t="n">
         <v>3136</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:25</t>
+          <t>2026-10-03 19:34:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:27</t>
+          <t>2026-10-03 19:34:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:29</t>
+          <t>2026-10-03 19:34:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 21:05:31</t>
+          <t>2026-10-03 19:34:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74003</v>
+        <v>4.73954</v>
       </c>
       <c r="G16" t="n">
-        <v>32832</v>
+        <v>32854</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="O16" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P16" t="n">
         <v>657</v>
       </c>
       <c r="Q16" t="n">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="R16" t="n">
-        <v>29220</v>
+        <v>29240</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:18</t>
+          <t>2026-10-04 19:50:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:21</t>
+          <t>2026-10-04 19:50:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81155</v>
+        <v>4.81134</v>
       </c>
       <c r="G3" t="n">
-        <v>13579</v>
+        <v>13596</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.3</t>
+          <t>4.46.4</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,11 +645,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>September 25, 2026</t>
+          <t>October 04, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O3" t="n">
         <v>136</v>
@@ -661,7 +661,7 @@
         <v>272</v>
       </c>
       <c r="R3" t="n">
-        <v>12628</v>
+        <v>12644</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:24</t>
+          <t>2026-10-04 19:50:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:26</t>
+          <t>2026-10-04 19:50:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85069</v>
+        <v>2.84896</v>
       </c>
       <c r="G5" t="n">
-        <v>3208</v>
+        <v>3211</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="O5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>96</v>
@@ -805,7 +805,7 @@
         <v>128</v>
       </c>
       <c r="R5" t="n">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:28</t>
+          <t>2026-10-04 19:50:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:31</t>
+          <t>2026-10-04 19:50:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:34</t>
+          <t>2026-10-04 19:50:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:36</t>
+          <t>2026-10-04 19:51:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60472</v>
+        <v>4.60417</v>
       </c>
       <c r="G9" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>5.1.3</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>August 16, 2026</t>
+          <t>October 04, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:38</t>
+          <t>2026-10-04 19:51:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:41</t>
+          <t>2026-10-04 19:51:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:44</t>
+          <t>2026-10-04 19:51:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71046</v>
+        <v>4.70896</v>
       </c>
       <c r="G12" t="n">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>157</v>
       </c>
       <c r="R12" t="n">
-        <v>2760</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:46</t>
+          <t>2026-10-04 19:51:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:48</t>
+          <t>2026-10-04 19:51:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.47177</v>
+        <v>3.46559</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:51</t>
+          <t>2026-10-04 19:51:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:53</t>
+          <t>2026-10-04 19:51:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73954</v>
+        <v>4.73951</v>
       </c>
       <c r="G16" t="n">
-        <v>32854</v>
+        <v>32869</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
@@ -1594,10 +1594,10 @@
         <v>657</v>
       </c>
       <c r="Q16" t="n">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="R16" t="n">
-        <v>29240</v>
+        <v>29253</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:41</t>
+          <t>2026-10-05 22:57:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:44</t>
+          <t>2026-10-05 22:58:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81134</v>
+        <v>4.81132</v>
       </c>
       <c r="G3" t="n">
-        <v>13596</v>
+        <v>13616</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>272</v>
       </c>
       <c r="R3" t="n">
-        <v>12644</v>
+        <v>12663</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:47</t>
+          <t>2026-10-05 22:58:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87446</v>
+        <v>3.87431</v>
       </c>
       <c r="G4" t="n">
-        <v>4867</v>
+        <v>4869</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.2</t>
+          <t>2.22.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -717,11 +717,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>September 08, 2026</t>
+          <t>October 05, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O4" t="n">
         <v>243</v>
@@ -730,10 +730,10 @@
         <v>243</v>
       </c>
       <c r="Q4" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="R4" t="n">
-        <v>3018</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:49</t>
+          <t>2026-10-05 22:58:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84896</v>
+        <v>2.84776</v>
       </c>
       <c r="G5" t="n">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="O5" t="n">
         <v>161</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:51</t>
+          <t>2026-10-05 22:58:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:54</t>
+          <t>2026-10-05 22:58:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>September 16, 2026</t>
+          <t>October 05, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:57</t>
+          <t>2026-10-05 22:58:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:00</t>
+          <t>2026-10-05 22:58:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60417</v>
+        <v>4.60523</v>
       </c>
       <c r="G9" t="n">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P9" t="n">
         <v>7</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:02</t>
+          <t>2026-10-05 22:58:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:05</t>
+          <t>2026-10-05 22:58:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:08</t>
+          <t>2026-10-05 22:58:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70896</v>
+        <v>4.70974</v>
       </c>
       <c r="G12" t="n">
-        <v>3137</v>
+        <v>3142</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O12" t="n">
         <v>31</v>
@@ -1309,7 +1309,7 @@
         <v>157</v>
       </c>
       <c r="R12" t="n">
-        <v>2729</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:10</t>
+          <t>2026-10-05 22:58:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:13</t>
+          <t>2026-10-05 22:58:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:15</t>
+          <t>2026-10-05 22:58:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-04 19:51:17</t>
+          <t>2026-10-05 22:58:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73951</v>
+        <v>4.7396</v>
       </c>
       <c r="G16" t="n">
-        <v>32869</v>
+        <v>32884</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>329</v>
       </c>
       <c r="P16" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q16" t="n">
         <v>1315</v>
       </c>
       <c r="R16" t="n">
-        <v>29253</v>
+        <v>29267</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:58</t>
+          <t>2026-10-06 21:20:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:00</t>
+          <t>2026-10-06 21:20:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:03</t>
+          <t>2026-10-06 21:20:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:05</t>
+          <t>2026-10-06 21:20:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:07</t>
+          <t>2026-10-06 21:20:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:10</t>
+          <t>2026-10-06 21:20:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:12</t>
+          <t>2026-10-06 21:20:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:15</t>
+          <t>2026-10-06 21:20:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:17</t>
+          <t>2026-10-06 21:20:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:20</t>
+          <t>2026-10-06 21:20:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:22</t>
+          <t>2026-10-06 21:20:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70974</v>
+        <v>4.70983</v>
       </c>
       <c r="G12" t="n">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:25</t>
+          <t>2026-10-06 21:20:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:28</t>
+          <t>2026-10-06 21:20:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:30</t>
+          <t>2026-10-06 21:20:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-05 22:58:33</t>
+          <t>2026-10-06 21:20:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7396</v>
+        <v>4.73955</v>
       </c>
       <c r="G16" t="n">
-        <v>32884</v>
+        <v>32886</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1315</v>
       </c>
       <c r="R16" t="n">
-        <v>29267</v>
+        <v>29269</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:06</t>
+          <t>2026-10-07 21:42:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:08</t>
+          <t>2026-10-07 21:42:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81132</v>
+        <v>4.81113</v>
       </c>
       <c r="G3" t="n">
-        <v>13616</v>
+        <v>13634</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O3" t="n">
         <v>136</v>
@@ -658,10 +658,10 @@
         <v>136</v>
       </c>
       <c r="Q3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R3" t="n">
-        <v>12663</v>
+        <v>12680</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:10</t>
+          <t>2026-10-07 21:42:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87431</v>
+        <v>3.87482</v>
       </c>
       <c r="G4" t="n">
-        <v>4869</v>
+        <v>4873</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="O4" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P4" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q4" t="n">
         <v>390</v>
       </c>
       <c r="R4" t="n">
-        <v>3019</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:12</t>
+          <t>2026-10-07 21:42:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84776</v>
+        <v>2.8456</v>
       </c>
       <c r="G5" t="n">
-        <v>3212</v>
+        <v>3219</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.6.8</t>
+          <t>10.7.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -789,23 +789,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>October 07, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="O5" t="n">
         <v>161</v>
       </c>
       <c r="P5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R5" t="n">
-        <v>1317</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:15</t>
+          <t>2026-10-07 21:42:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.31183</v>
+        <v>3.29947</v>
       </c>
       <c r="G6" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -877,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:17</t>
+          <t>2026-10-07 21:42:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98422</v>
+        <v>3.98476</v>
       </c>
       <c r="G7" t="n">
-        <v>3803</v>
+        <v>3805</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>190</v>
       </c>
       <c r="Q7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>2396</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:19</t>
+          <t>2026-10-07 21:42:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:22</t>
+          <t>2026-10-07 21:42:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60523</v>
+        <v>4.60576</v>
       </c>
       <c r="G9" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:24</t>
+          <t>2026-10-07 21:42:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:26</t>
+          <t>2026-10-07 21:42:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:28</t>
+          <t>2026-10-07 21:42:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70983</v>
+        <v>4.7062</v>
       </c>
       <c r="G12" t="n">
-        <v>3143</v>
+        <v>3145</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>157</v>
       </c>
       <c r="R12" t="n">
-        <v>2734</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:31</t>
+          <t>2026-10-07 21:42:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:33</t>
+          <t>2026-10-07 21:42:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:35</t>
+          <t>2026-10-07 21:43:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:37</t>
+          <t>2026-10-07 21:43:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73955</v>
+        <v>4.73918</v>
       </c>
       <c r="G16" t="n">
-        <v>32886</v>
+        <v>32908</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
@@ -1594,10 +1594,10 @@
         <v>658</v>
       </c>
       <c r="Q16" t="n">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="R16" t="n">
-        <v>29269</v>
+        <v>29288</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:30</t>
+          <t>2026-10-08 21:36:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:32</t>
+          <t>2026-10-08 21:36:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81113</v>
+        <v>4.81043</v>
       </c>
       <c r="G3" t="n">
-        <v>13634</v>
+        <v>13652</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q3" t="n">
         <v>273</v>
       </c>
       <c r="R3" t="n">
-        <v>12680</v>
+        <v>12696</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:35</t>
+          <t>2026-10-08 21:36:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87482</v>
+        <v>3.87446</v>
       </c>
       <c r="G4" t="n">
-        <v>4873</v>
+        <v>4875</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>390</v>
       </c>
       <c r="R4" t="n">
-        <v>3021</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:37</t>
+          <t>2026-10-08 21:36:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8456</v>
+        <v>2.84513</v>
       </c>
       <c r="G5" t="n">
-        <v>3219</v>
+        <v>3222</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="O5" t="n">
         <v>161</v>
@@ -805,7 +805,7 @@
         <v>129</v>
       </c>
       <c r="R5" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:39</t>
+          <t>2026-10-08 21:36:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:42</t>
+          <t>2026-10-08 21:36:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:44</t>
+          <t>2026-10-08 21:36:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:46</t>
+          <t>2026-10-08 21:36:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:49</t>
+          <t>2026-10-08 21:36:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:52</t>
+          <t>2026-10-08 21:36:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:54</t>
+          <t>2026-10-08 21:36:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7062</v>
+        <v>4.70599</v>
       </c>
       <c r="G12" t="n">
-        <v>3145</v>
+        <v>3153</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1300,16 +1300,16 @@
         <v>126</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12" t="n">
         <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2736</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:56</t>
+          <t>2026-10-08 21:36:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:59</t>
+          <t>2026-10-08 21:36:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-07 21:43:01</t>
+          <t>2026-10-08 21:36:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-07 21:43:03</t>
+          <t>2026-10-08 21:36:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73918</v>
+        <v>4.73933</v>
       </c>
       <c r="G16" t="n">
-        <v>32908</v>
+        <v>32931</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
       </c>
       <c r="P16" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Q16" t="n">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="R16" t="n">
-        <v>29288</v>
+        <v>29309</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:07</t>
+          <t>2026-10-09 21:22:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:10</t>
+          <t>2026-10-09 21:22:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81043</v>
+        <v>4.81058</v>
       </c>
       <c r="G3" t="n">
-        <v>13652</v>
+        <v>13663</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>273</v>
       </c>
       <c r="R3" t="n">
-        <v>12696</v>
+        <v>12707</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:12</t>
+          <t>2026-10-09 21:22:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:15</t>
+          <t>2026-10-09 21:22:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84513</v>
+        <v>2.84522</v>
       </c>
       <c r="G5" t="n">
-        <v>3222</v>
+        <v>3224</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="O5" t="n">
         <v>161</v>
@@ -805,7 +805,7 @@
         <v>129</v>
       </c>
       <c r="R5" t="n">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:17</t>
+          <t>2026-10-09 21:22:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:19</t>
+          <t>2026-10-09 21:22:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:22</t>
+          <t>2026-10-09 21:22:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:24</t>
+          <t>2026-10-09 21:22:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:27</t>
+          <t>2026-10-09 21:22:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:29</t>
+          <t>2026-10-09 21:22:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:31</t>
+          <t>2026-10-09 21:22:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70599</v>
+        <v>4.7045</v>
       </c>
       <c r="G12" t="n">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2743</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:33</t>
+          <t>2026-10-09 21:22:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:35</t>
+          <t>2026-10-09 21:22:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:37</t>
+          <t>2026-10-09 21:22:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:40</t>
+          <t>2026-10-09 21:22:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73933</v>
+        <v>4.73926</v>
       </c>
       <c r="G16" t="n">
-        <v>32931</v>
+        <v>32948</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
@@ -1594,10 +1594,10 @@
         <v>659</v>
       </c>
       <c r="Q16" t="n">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="R16" t="n">
-        <v>29309</v>
+        <v>29324</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:16</t>
+          <t>2026-10-10 20:22:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:19</t>
+          <t>2026-10-10 20:22:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81058</v>
+        <v>4.81041</v>
       </c>
       <c r="G3" t="n">
-        <v>13663</v>
+        <v>13672</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>273</v>
       </c>
       <c r="R3" t="n">
-        <v>12707</v>
+        <v>12715</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:21</t>
+          <t>2026-10-10 20:22:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:24</t>
+          <t>2026-10-10 20:22:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84522</v>
+        <v>2.84646</v>
       </c>
       <c r="G5" t="n">
         <v>3224</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:26</t>
+          <t>2026-10-10 20:22:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:28</t>
+          <t>2026-10-10 20:22:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98476</v>
+        <v>3.98556</v>
       </c>
       <c r="G7" t="n">
-        <v>3805</v>
+        <v>3808</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>2397</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:31</t>
+          <t>2026-10-10 20:22:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:34</t>
+          <t>2026-10-10 20:22:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:37</t>
+          <t>2026-10-10 20:22:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:39</t>
+          <t>2026-10-10 20:22:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:42</t>
+          <t>2026-10-10 20:22:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7045</v>
+        <v>4.70586</v>
       </c>
       <c r="G12" t="n">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2744</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:44</t>
+          <t>2026-10-10 20:22:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:46</t>
+          <t>2026-10-10 20:22:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:48</t>
+          <t>2026-10-10 20:22:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:51</t>
+          <t>2026-10-10 20:22:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73926</v>
+        <v>4.73905</v>
       </c>
       <c r="G16" t="n">
-        <v>32948</v>
+        <v>32953</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1318</v>
       </c>
       <c r="O16" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P16" t="n">
         <v>659</v>
@@ -1597,7 +1597,7 @@
         <v>1318</v>
       </c>
       <c r="R16" t="n">
-        <v>29324</v>
+        <v>29328</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:11</t>
+          <t>2026-10-11 20:39:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:13</t>
+          <t>2026-10-11 20:39:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81041</v>
+        <v>4.81066</v>
       </c>
       <c r="G3" t="n">
-        <v>13672</v>
+        <v>13690</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O3" t="n">
         <v>137</v>
@@ -658,10 +658,10 @@
         <v>137</v>
       </c>
       <c r="Q3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R3" t="n">
-        <v>12715</v>
+        <v>12732</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:16</t>
+          <t>2026-10-11 20:39:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87446</v>
+        <v>3.87387</v>
       </c>
       <c r="G4" t="n">
-        <v>4875</v>
+        <v>4876</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>390</v>
       </c>
       <c r="R4" t="n">
-        <v>3022</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:18</t>
+          <t>2026-10-11 20:39:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84646</v>
+        <v>2.84542</v>
       </c>
       <c r="G5" t="n">
-        <v>3224</v>
+        <v>3228</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="O5" t="n">
         <v>161</v>
@@ -805,7 +805,7 @@
         <v>129</v>
       </c>
       <c r="R5" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:20</t>
+          <t>2026-10-11 20:39:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:23</t>
+          <t>2026-10-11 20:39:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>3.98556</v>
       </c>
       <c r="G7" t="n">
-        <v>3808</v>
+        <v>3809</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O7" t="n">
         <v>152</v>
@@ -949,7 +949,7 @@
         <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:25</t>
+          <t>2026-10-11 20:39:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:27</t>
+          <t>2026-10-11 20:39:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:30</t>
+          <t>2026-10-11 20:39:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.88638</v>
+        <v>3.88722</v>
       </c>
       <c r="G10" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.29</t>
+          <t>2.1.30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>September 02, 2026</t>
+          <t>October 11, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:32</t>
+          <t>2026-10-11 20:40:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:35</t>
+          <t>2026-10-11 20:40:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70586</v>
+        <v>4.70596</v>
       </c>
       <c r="G12" t="n">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2745</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:37</t>
+          <t>2026-10-11 20:40:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:39</t>
+          <t>2026-10-11 20:40:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:42</t>
+          <t>2026-10-11 20:40:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:44</t>
+          <t>2026-10-11 20:40:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73905</v>
+        <v>4.73945</v>
       </c>
       <c r="G16" t="n">
-        <v>32953</v>
+        <v>32969</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="O16" t="n">
         <v>330</v>
@@ -1594,10 +1594,10 @@
         <v>659</v>
       </c>
       <c r="Q16" t="n">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="R16" t="n">
-        <v>29328</v>
+        <v>29342</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:35</t>
+          <t>2026-10-12 23:18:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:38</t>
+          <t>2026-10-12 23:18:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81066</v>
+        <v>4.81023</v>
       </c>
       <c r="G3" t="n">
-        <v>13690</v>
+        <v>13701</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>274</v>
       </c>
       <c r="R3" t="n">
-        <v>12732</v>
+        <v>12742</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:41</t>
+          <t>2026-10-12 23:18:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87387</v>
+        <v>3.87436</v>
       </c>
       <c r="G4" t="n">
-        <v>4876</v>
+        <v>4879</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="O4" t="n">
         <v>244</v>
@@ -733,7 +733,7 @@
         <v>390</v>
       </c>
       <c r="R4" t="n">
-        <v>3023</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:43</t>
+          <t>2026-10-12 23:18:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84542</v>
+        <v>2.84848</v>
       </c>
       <c r="G5" t="n">
-        <v>3228</v>
+        <v>3234</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P5" t="n">
         <v>97</v>
@@ -805,7 +805,7 @@
         <v>129</v>
       </c>
       <c r="R5" t="n">
-        <v>1323</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:45</t>
+          <t>2026-10-12 23:18:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:50</t>
+          <t>2026-10-12 23:18:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98556</v>
+        <v>3.98583</v>
       </c>
       <c r="G7" t="n">
-        <v>3809</v>
+        <v>3810</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:52</t>
+          <t>2026-10-12 23:18:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:55</t>
+          <t>2026-10-12 23:19:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:58</t>
+          <t>2026-10-12 23:19:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.88722</v>
+        <v>3.89366</v>
       </c>
       <c r="G10" t="n">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="O10" t="n">
         <v>43</v>
@@ -1165,7 +1165,7 @@
         <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-11 20:40:01</t>
+          <t>2026-10-12 23:19:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-11 20:40:06</t>
+          <t>2026-10-12 23:19:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70596</v>
+        <v>4.70646</v>
       </c>
       <c r="G12" t="n">
-        <v>3156</v>
+        <v>3158</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>September 21, 2026</t>
+          <t>October 12, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2746</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-11 20:40:09</t>
+          <t>2026-10-12 23:19:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-11 20:40:11</t>
+          <t>2026-10-12 23:19:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.46559</v>
+        <v>3.47177</v>
       </c>
       <c r="G14" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-11 20:40:14</t>
+          <t>2026-10-12 23:19:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-11 20:40:17</t>
+          <t>2026-10-12 23:19:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73945</v>
+        <v>4.73914</v>
       </c>
       <c r="G16" t="n">
-        <v>32969</v>
+        <v>32983</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>330</v>
       </c>
       <c r="P16" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q16" t="n">
         <v>1319</v>
       </c>
       <c r="R16" t="n">
-        <v>29342</v>
+        <v>29355</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:43</t>
+          <t>2026-10-13 21:36:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:46</t>
+          <t>2026-10-13 21:36:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81023</v>
+        <v>4.81034</v>
       </c>
       <c r="G3" t="n">
-        <v>13701</v>
+        <v>13709</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>274</v>
       </c>
       <c r="R3" t="n">
-        <v>12742</v>
+        <v>12749</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:49</t>
+          <t>2026-10-13 21:36:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:51</t>
+          <t>2026-10-13 21:36:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84848</v>
+        <v>2.84708</v>
       </c>
       <c r="G5" t="n">
-        <v>3234</v>
+        <v>3237</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="O5" t="n">
         <v>162</v>
@@ -805,7 +805,7 @@
         <v>129</v>
       </c>
       <c r="R5" t="n">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:54</t>
+          <t>2026-10-13 21:36:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:57</t>
+          <t>2026-10-13 21:37:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98583</v>
+        <v>3.98609</v>
       </c>
       <c r="G7" t="n">
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>152</v>
       </c>
       <c r="P7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q7" t="n">
         <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>2400</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:59</t>
+          <t>2026-10-13 21:37:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:02</t>
+          <t>2026-10-13 21:37:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:04</t>
+          <t>2026-10-13 21:37:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89366</v>
+        <v>3.89239</v>
       </c>
       <c r="G10" t="n">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O10" t="n">
         <v>43</v>
@@ -1162,10 +1162,10 @@
         <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:07</t>
+          <t>2026-10-13 21:37:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:09</t>
+          <t>2026-10-13 21:37:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70646</v>
+        <v>4.70614</v>
       </c>
       <c r="G12" t="n">
         <v>3158</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>October 12, 2026</t>
+          <t>October 13, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:12</t>
+          <t>2026-10-13 21:37:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:14</t>
+          <t>2026-10-13 21:37:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:17</t>
+          <t>2026-10-13 21:37:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-12 23:19:19</t>
+          <t>2026-10-13 21:37:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73914</v>
+        <v>4.73898</v>
       </c>
       <c r="G16" t="n">
-        <v>32983</v>
+        <v>32990</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="O16" t="n">
         <v>330</v>
@@ -1594,10 +1594,10 @@
         <v>660</v>
       </c>
       <c r="Q16" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="R16" t="n">
-        <v>29355</v>
+        <v>29361</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:47</t>
+          <t>2026-10-14 20:22:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:50</t>
+          <t>2026-10-14 20:22:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81034</v>
+        <v>4.81011</v>
       </c>
       <c r="G3" t="n">
-        <v>13709</v>
+        <v>13729</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O3" t="n">
         <v>137</v>
@@ -658,10 +658,10 @@
         <v>137</v>
       </c>
       <c r="Q3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R3" t="n">
-        <v>12749</v>
+        <v>12768</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:53</t>
+          <t>2026-10-14 20:22:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87436</v>
+        <v>3.87459</v>
       </c>
       <c r="G4" t="n">
-        <v>4879</v>
+        <v>4880</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>390</v>
       </c>
       <c r="R4" t="n">
-        <v>3025</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:55</t>
+          <t>2026-10-14 20:22:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84708</v>
+        <v>2.84793</v>
       </c>
       <c r="G5" t="n">
-        <v>3237</v>
+        <v>3242</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="O5" t="n">
         <v>162</v>
@@ -802,10 +802,10 @@
         <v>97</v>
       </c>
       <c r="Q5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R5" t="n">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:58</t>
+          <t>2026-10-14 20:22:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.29947</v>
+        <v>3.28723</v>
       </c>
       <c r="G6" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:00</t>
+          <t>2026-10-14 20:22:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:03</t>
+          <t>2026-10-14 20:22:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:05</t>
+          <t>2026-10-14 20:23:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:08</t>
+          <t>2026-10-14 20:23:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89239</v>
+        <v>3.89444</v>
       </c>
       <c r="G10" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.30</t>
+          <t>2.1.31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>October 11, 2026</t>
+          <t>October 14, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O10" t="n">
         <v>43</v>
@@ -1165,7 +1165,7 @@
         <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:10</t>
+          <t>2026-10-14 20:23:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.60784</v>
+        <v>2.57692</v>
       </c>
       <c r="G11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:13</t>
+          <t>2026-10-14 20:23:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70614</v>
+        <v>4.70625</v>
       </c>
       <c r="G12" t="n">
-        <v>3158</v>
+        <v>3166</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O12" t="n">
         <v>32</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2747</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:15</t>
+          <t>2026-10-14 20:23:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:18</t>
+          <t>2026-10-14 20:23:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:20</t>
+          <t>2026-10-14 20:23:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-13 21:37:23</t>
+          <t>2026-10-14 20:23:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73898</v>
+        <v>4.73885</v>
       </c>
       <c r="G16" t="n">
-        <v>32990</v>
+        <v>33015</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="O16" t="n">
         <v>330</v>
@@ -1594,10 +1594,10 @@
         <v>660</v>
       </c>
       <c r="Q16" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="R16" t="n">
-        <v>29361</v>
+        <v>29383</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:44</t>
+          <t>2026-10-15 20:06:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:46</t>
+          <t>2026-10-15 20:06:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81011</v>
+        <v>4.80992</v>
       </c>
       <c r="G3" t="n">
-        <v>13729</v>
+        <v>13737</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>275</v>
       </c>
       <c r="R3" t="n">
-        <v>12768</v>
+        <v>12775</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:49</t>
+          <t>2026-10-15 20:06:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87459</v>
+        <v>3.87423</v>
       </c>
       <c r="G4" t="n">
-        <v>4880</v>
+        <v>4882</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -730,10 +730,10 @@
         <v>244</v>
       </c>
       <c r="Q4" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>3026</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:51</t>
+          <t>2026-10-15 20:06:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84793</v>
+        <v>2.84679</v>
       </c>
       <c r="G5" t="n">
-        <v>3242</v>
+        <v>3244</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="O5" t="n">
         <v>162</v>
@@ -805,7 +805,7 @@
         <v>130</v>
       </c>
       <c r="R5" t="n">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:53</t>
+          <t>2026-10-15 20:06:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:56</t>
+          <t>2026-10-15 20:06:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:58</t>
+          <t>2026-10-15 20:06:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:00</t>
+          <t>2026-10-15 20:06:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60576</v>
+        <v>4.6063</v>
       </c>
       <c r="G9" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:02</t>
+          <t>2026-10-15 20:06:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89444</v>
+        <v>3.8962</v>
       </c>
       <c r="G10" t="n">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.31</t>
+          <t>2.1.32</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>October 14, 2026</t>
+          <t>October 15, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1165,7 +1165,7 @@
         <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:04</t>
+          <t>2026-10-15 20:06:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:07</t>
+          <t>2026-10-15 20:06:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70625</v>
+        <v>4.70498</v>
       </c>
       <c r="G12" t="n">
         <v>3166</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:09</t>
+          <t>2026-10-15 20:06:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.99828</v>
+        <v>3.99312</v>
       </c>
       <c r="G13" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:11</t>
+          <t>2026-10-15 20:06:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:14</t>
+          <t>2026-10-15 20:06:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 20:23:16</t>
+          <t>2026-10-15 20:06:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73885</v>
+        <v>4.73848</v>
       </c>
       <c r="G16" t="n">
-        <v>33015</v>
+        <v>33031</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>330</v>
       </c>
       <c r="P16" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Q16" t="n">
         <v>1321</v>
       </c>
       <c r="R16" t="n">
-        <v>29383</v>
+        <v>29398</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:12</t>
+          <t>2026-10-16 19:45:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:14</t>
+          <t>2026-10-16 19:45:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.4</t>
+          <t>4.46.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>October 04, 2026</t>
+          <t>October 16, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:18</t>
+          <t>2026-10-16 19:45:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:20</t>
+          <t>2026-10-16 19:45:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:22</t>
+          <t>2026-10-16 19:45:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:25</t>
+          <t>2026-10-16 19:45:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:30</t>
+          <t>2026-10-16 19:45:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:33</t>
+          <t>2026-10-16 19:45:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:36</t>
+          <t>2026-10-16 19:45:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:39</t>
+          <t>2026-10-16 19:45:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:41</t>
+          <t>2026-10-16 19:45:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:43</t>
+          <t>2026-10-16 19:45:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:46</t>
+          <t>2026-10-16 19:45:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:48</t>
+          <t>2026-10-16 19:45:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:51</t>
+          <t>2026-10-16 19:45:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:14</t>
+          <t>2026-10-17 18:55:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:17</t>
+          <t>2026-10-17 18:55:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80992</v>
+        <v>4.80952</v>
       </c>
       <c r="G3" t="n">
-        <v>13737</v>
+        <v>13761</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q3" t="n">
         <v>275</v>
       </c>
       <c r="R3" t="n">
-        <v>12775</v>
+        <v>12798</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:20</t>
+          <t>2026-10-17 18:55:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87423</v>
+        <v>3.87446</v>
       </c>
       <c r="G4" t="n">
-        <v>4882</v>
+        <v>4883</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="O4" t="n">
         <v>244</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:22</t>
+          <t>2026-10-17 18:55:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84679</v>
+        <v>2.84405</v>
       </c>
       <c r="G5" t="n">
-        <v>3244</v>
+        <v>3251</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="O5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="n">
         <v>130</v>
       </c>
       <c r="R5" t="n">
-        <v>1330</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:24</t>
+          <t>2026-10-17 18:55:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.28723</v>
+        <v>3.29101</v>
       </c>
       <c r="G6" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -877,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:26</t>
+          <t>2026-10-17 18:55:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98609</v>
+        <v>3.98715</v>
       </c>
       <c r="G7" t="n">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:29</t>
+          <t>2026-10-17 18:55:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>September 01, 2026</t>
+          <t>October 17, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:31</t>
+          <t>2026-10-17 18:55:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6063</v>
+        <v>4.60576</v>
       </c>
       <c r="G9" t="n">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:33</t>
+          <t>2026-10-17 18:55:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8962</v>
+        <v>3.89576</v>
       </c>
       <c r="G10" t="n">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O10" t="n">
         <v>43</v>
@@ -1165,7 +1165,7 @@
         <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:36</t>
+          <t>2026-10-17 18:55:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:39</t>
+          <t>2026-10-17 18:55:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70498</v>
+        <v>4.70401</v>
       </c>
       <c r="G12" t="n">
-        <v>3166</v>
+        <v>3169</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="R12" t="n">
-        <v>2754</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:41</t>
+          <t>2026-10-17 18:55:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.99312</v>
+        <v>3.99314</v>
       </c>
       <c r="G13" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O13" t="n">
         <v>23</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:43</t>
+          <t>2026-10-17 18:55:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:46</t>
+          <t>2026-10-17 18:55:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:48</t>
+          <t>2026-10-17 18:55:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73848</v>
+        <v>4.73812</v>
       </c>
       <c r="G16" t="n">
-        <v>33031</v>
+        <v>33046</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="O16" t="n">
         <v>330</v>
@@ -1594,10 +1594,10 @@
         <v>661</v>
       </c>
       <c r="Q16" t="n">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="R16" t="n">
-        <v>29398</v>
+        <v>29411</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:11</t>
+          <t>2026-10-18 19:02:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:13</t>
+          <t>2026-10-18 19:03:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80952</v>
+        <v>4.80942</v>
       </c>
       <c r="G3" t="n">
-        <v>13761</v>
+        <v>13774</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>275</v>
       </c>
       <c r="R3" t="n">
-        <v>12798</v>
+        <v>12810</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:16</t>
+          <t>2026-10-18 19:03:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:18</t>
+          <t>2026-10-18 19:03:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84405</v>
+        <v>2.84209</v>
       </c>
       <c r="G5" t="n">
-        <v>3251</v>
+        <v>3255</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="O5" t="n">
         <v>163</v>
@@ -805,7 +805,7 @@
         <v>130</v>
       </c>
       <c r="R5" t="n">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:20</t>
+          <t>2026-10-18 19:03:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.29101</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:23</t>
+          <t>2026-10-18 19:03:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98715</v>
+        <v>3.98741</v>
       </c>
       <c r="G7" t="n">
-        <v>3812</v>
+        <v>3813</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>648</v>
       </c>
       <c r="O7" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P7" t="n">
         <v>191</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:25</t>
+          <t>2026-10-18 19:03:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74191</v>
+        <v>4.74185</v>
       </c>
       <c r="G8" t="n">
-        <v>13627</v>
+        <v>13624</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12128</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:27</t>
+          <t>2026-10-18 19:03:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:30</t>
+          <t>2026-10-18 19:03:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89576</v>
+        <v>3.89614</v>
       </c>
       <c r="G10" t="n">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1156,16 +1156,16 @@
         <v>228</v>
       </c>
       <c r="O10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="n">
         <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:32</t>
+          <t>2026-10-18 19:03:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:35</t>
+          <t>2026-10-18 19:03:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70401</v>
+        <v>4.70407</v>
       </c>
       <c r="G12" t="n">
-        <v>3169</v>
+        <v>3173</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R12" t="n">
-        <v>2757</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:37</t>
+          <t>2026-10-18 19:03:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.99314</v>
+        <v>3.99656</v>
       </c>
       <c r="G13" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:39</t>
+          <t>2026-10-18 19:03:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:42</t>
+          <t>2026-10-18 19:03:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:44</t>
+          <t>2026-10-18 19:03:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73812</v>
+        <v>4.73806</v>
       </c>
       <c r="G16" t="n">
-        <v>33046</v>
+        <v>33061</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.7</t>
+          <t>3.1.8</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>September 14, 2026</t>
+          <t>October 18, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>1322</v>
       </c>
       <c r="O16" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P16" t="n">
         <v>661</v>
@@ -1597,7 +1597,7 @@
         <v>1322</v>
       </c>
       <c r="R16" t="n">
-        <v>29411</v>
+        <v>29424</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:58</t>
+          <t>2026-10-19 21:17:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:00</t>
+          <t>2026-10-19 21:17:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80942</v>
+        <v>4.80952</v>
       </c>
       <c r="G3" t="n">
-        <v>13774</v>
+        <v>13787</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O3" t="n">
         <v>138</v>
@@ -658,10 +658,10 @@
         <v>138</v>
       </c>
       <c r="Q3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R3" t="n">
-        <v>12810</v>
+        <v>12822</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:02</t>
+          <t>2026-10-19 21:17:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87446</v>
+        <v>3.87469</v>
       </c>
       <c r="G4" t="n">
-        <v>4883</v>
+        <v>4884</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>3027</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:04</t>
+          <t>2026-10-19 21:17:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84209</v>
+        <v>2.84285</v>
       </c>
       <c r="G5" t="n">
-        <v>3255</v>
+        <v>3258</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="O5" t="n">
         <v>163</v>
@@ -805,7 +805,7 @@
         <v>130</v>
       </c>
       <c r="R5" t="n">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:07</t>
+          <t>2026-10-19 21:18:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:09</t>
+          <t>2026-10-19 21:18:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.4</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>October 05, 2026</t>
+          <t>October 19, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:11</t>
+          <t>2026-10-19 21:18:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74185</v>
+        <v>4.74191</v>
       </c>
       <c r="G8" t="n">
-        <v>13624</v>
+        <v>13627</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12125</v>
+        <v>12128</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:13</t>
+          <t>2026-10-19 21:18:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:15</t>
+          <t>2026-10-19 21:18:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89614</v>
+        <v>3.89817</v>
       </c>
       <c r="G10" t="n">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O10" t="n">
         <v>44</v>
@@ -1165,7 +1165,7 @@
         <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:17</t>
+          <t>2026-10-19 21:18:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:20</t>
+          <t>2026-10-19 21:18:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70407</v>
+        <v>4.70622</v>
       </c>
       <c r="G12" t="n">
-        <v>3173</v>
+        <v>3176</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="P12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q12" t="n">
         <v>159</v>
       </c>
       <c r="R12" t="n">
-        <v>2761</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:22</t>
+          <t>2026-10-19 21:18:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.99656</v>
+        <v>3.99485</v>
       </c>
       <c r="G13" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:24</t>
+          <t>2026-10-19 21:18:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:26</t>
+          <t>2026-10-19 21:18:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-18 19:03:28</t>
+          <t>2026-10-19 21:18:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73806</v>
+        <v>4.73794</v>
       </c>
       <c r="G16" t="n">
-        <v>33061</v>
+        <v>33080</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O16" t="n">
         <v>331</v>
       </c>
       <c r="P16" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Q16" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="R16" t="n">
-        <v>29424</v>
+        <v>29441</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:51</t>
+          <t>2026-10-20 20:11:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:53</t>
+          <t>2026-10-20 20:11:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80952</v>
+        <v>4.80957</v>
       </c>
       <c r="G3" t="n">
-        <v>13787</v>
+        <v>13790</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>276</v>
       </c>
       <c r="R3" t="n">
-        <v>12822</v>
+        <v>12825</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:56</t>
+          <t>2026-10-20 20:11:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:58</t>
+          <t>2026-10-20 20:11:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84285</v>
+        <v>2.84351</v>
       </c>
       <c r="G5" t="n">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.7.3</t>
+          <t>10.7.5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>October 07, 2026</t>
+          <t>October 20, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:01</t>
+          <t>2026-10-20 20:11:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:04</t>
+          <t>2026-10-20 20:12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98741</v>
+        <v>3.98742</v>
       </c>
       <c r="G7" t="n">
-        <v>3813</v>
+        <v>3815</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O7" t="n">
         <v>153</v>
@@ -946,10 +946,10 @@
         <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R7" t="n">
-        <v>2402</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:07</t>
+          <t>2026-10-20 20:12:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:09</t>
+          <t>2026-10-20 20:12:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:12</t>
+          <t>2026-10-20 20:12:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89817</v>
+        <v>3.89918</v>
       </c>
       <c r="G10" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>65</v>
       </c>
       <c r="R10" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:14</t>
+          <t>2026-10-20 20:12:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:17</t>
+          <t>2026-10-20 20:12:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70622</v>
+        <v>4.70633</v>
       </c>
       <c r="G12" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>159</v>
       </c>
       <c r="R12" t="n">
-        <v>2763</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:20</t>
+          <t>2026-10-20 20:12:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:22</t>
+          <t>2026-10-20 20:12:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>September 20, 2026</t>
+          <t>October 20, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:25</t>
+          <t>2026-10-20 20:12:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-19 21:18:28</t>
+          <t>2026-10-20 20:12:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73794</v>
+        <v>4.73787</v>
       </c>
       <c r="G16" t="n">
-        <v>33080</v>
+        <v>33091</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.8</t>
+          <t>3.1.9</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,11 +1581,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>October 18, 2026</t>
+          <t>October 19, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="O16" t="n">
         <v>331</v>
@@ -1594,10 +1594,10 @@
         <v>662</v>
       </c>
       <c r="Q16" t="n">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="R16" t="n">
-        <v>29441</v>
+        <v>29451</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:48</t>
+          <t>2026-10-21 20:24:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:51</t>
+          <t>2026-10-21 20:24:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80957</v>
+        <v>4.80975</v>
       </c>
       <c r="G3" t="n">
-        <v>13790</v>
+        <v>13803</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>276</v>
       </c>
       <c r="R3" t="n">
-        <v>12825</v>
+        <v>12837</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:53</t>
+          <t>2026-10-21 20:24:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:56</t>
+          <t>2026-10-21 20:24:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84351</v>
+        <v>2.84375</v>
       </c>
       <c r="G5" t="n">
-        <v>3259</v>
+        <v>3264</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="O5" t="n">
         <v>163</v>
@@ -802,10 +802,10 @@
         <v>98</v>
       </c>
       <c r="Q5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R5" t="n">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:58</t>
+          <t>2026-10-21 20:24:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:00</t>
+          <t>2026-10-21 20:24:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98742</v>
+        <v>3.98716</v>
       </c>
       <c r="G7" t="n">
-        <v>3815</v>
+        <v>3817</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>420</v>
       </c>
       <c r="R7" t="n">
-        <v>2403</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:04</t>
+          <t>2026-10-21 20:24:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:07</t>
+          <t>2026-10-21 20:24:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.60576</v>
+        <v>4.60357</v>
       </c>
       <c r="G9" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:09</t>
+          <t>2026-10-21 20:24:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:11</t>
+          <t>2026-10-21 20:24:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:14</t>
+          <t>2026-10-21 20:24:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70633</v>
+        <v>4.7049</v>
       </c>
       <c r="G12" t="n">
-        <v>3177</v>
+        <v>3182</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>October 13, 2026</t>
+          <t>October 20, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>159</v>
       </c>
       <c r="R12" t="n">
-        <v>2764</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:16</t>
+          <t>2026-10-21 20:24:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:18</t>
+          <t>2026-10-21 20:24:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:21</t>
+          <t>2026-10-21 20:24:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 20:12:23</t>
+          <t>2026-10-21 20:24:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73787</v>
+        <v>4.73818</v>
       </c>
       <c r="G16" t="n">
-        <v>33091</v>
+        <v>33107</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1324</v>
       </c>
       <c r="R16" t="n">
-        <v>29451</v>
+        <v>29465</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:09</t>
+          <t>2026-10-22 20:50:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:12</t>
+          <t>2026-10-22 20:50:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80975</v>
+        <v>4.80949</v>
       </c>
       <c r="G3" t="n">
-        <v>13803</v>
+        <v>13805</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>276</v>
       </c>
       <c r="R3" t="n">
-        <v>12837</v>
+        <v>12839</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:14</t>
+          <t>2026-10-22 20:50:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:17</t>
+          <t>2026-10-22 20:50:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84375</v>
+        <v>2.84302</v>
       </c>
       <c r="G5" t="n">
-        <v>3264</v>
+        <v>3268</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="O5" t="n">
         <v>163</v>
@@ -805,7 +805,7 @@
         <v>131</v>
       </c>
       <c r="R5" t="n">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:19</t>
+          <t>2026-10-22 20:50:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:22</t>
+          <t>2026-10-22 20:50:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98716</v>
+        <v>3.98507</v>
       </c>
       <c r="G7" t="n">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:24</t>
+          <t>2026-10-22 20:51:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:26</t>
+          <t>2026-10-22 20:51:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:29</t>
+          <t>2026-10-22 20:51:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:31</t>
+          <t>2026-10-22 20:51:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:33</t>
+          <t>2026-10-22 20:51:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7049</v>
+        <v>4.70509</v>
       </c>
       <c r="G12" t="n">
-        <v>3182</v>
+        <v>3184</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.0.2</t>
+          <t>3.0.3</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>October 20, 2026</t>
+          <t>October 22, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>159</v>
       </c>
       <c r="R12" t="n">
-        <v>2768</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:36</t>
+          <t>2026-10-22 20:51:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:38</t>
+          <t>2026-10-22 20:51:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>October 20, 2026</t>
+          <t>October 22, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:41</t>
+          <t>2026-10-22 20:51:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:43</t>
+          <t>2026-10-22 20:51:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73818</v>
+        <v>4.73792</v>
       </c>
       <c r="G16" t="n">
-        <v>33107</v>
+        <v>33123</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="O16" t="n">
         <v>331</v>
@@ -1594,10 +1594,10 @@
         <v>662</v>
       </c>
       <c r="Q16" t="n">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="R16" t="n">
-        <v>29465</v>
+        <v>29479</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:47</t>
+          <t>2026-10-23 20:08:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:49</t>
+          <t>2026-10-23 20:08:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80949</v>
+        <v>4.80942</v>
       </c>
       <c r="G3" t="n">
-        <v>13805</v>
+        <v>13821</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O3" t="n">
         <v>138</v>
@@ -661,7 +661,7 @@
         <v>276</v>
       </c>
       <c r="R3" t="n">
-        <v>12839</v>
+        <v>12854</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:52</t>
+          <t>2026-10-23 20:08:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:54</t>
+          <t>2026-10-23 20:08:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84302</v>
+        <v>2.83293</v>
       </c>
       <c r="G5" t="n">
-        <v>3268</v>
+        <v>3298</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1569</v>
+        <v>1583</v>
       </c>
       <c r="O5" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R5" t="n">
-        <v>1340</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:56</t>
+          <t>2026-10-23 20:08:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:58</t>
+          <t>2026-10-23 20:08:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98507</v>
+        <v>3.98614</v>
       </c>
       <c r="G7" t="n">
-        <v>3818</v>
+        <v>3823</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O7" t="n">
         <v>153</v>
@@ -946,10 +946,10 @@
         <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R7" t="n">
-        <v>2405</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:01</t>
+          <t>2026-10-23 20:09:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74191</v>
+        <v>4.74189</v>
       </c>
       <c r="G8" t="n">
-        <v>13627</v>
+        <v>13626</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12128</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:03</t>
+          <t>2026-10-23 20:09:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:05</t>
+          <t>2026-10-23 20:09:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:08</t>
+          <t>2026-10-23 20:09:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:10</t>
+          <t>2026-10-23 20:09:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70509</v>
+        <v>4.70273</v>
       </c>
       <c r="G12" t="n">
-        <v>3184</v>
+        <v>3189</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O12" t="n">
         <v>32</v>
@@ -1309,7 +1309,7 @@
         <v>159</v>
       </c>
       <c r="R12" t="n">
-        <v>2770</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:12</t>
+          <t>2026-10-23 20:09:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:14</t>
+          <t>2026-10-23 20:09:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:17</t>
+          <t>2026-10-23 20:09:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-22 20:51:19</t>
+          <t>2026-10-23 20:09:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73792</v>
+        <v>4.73775</v>
       </c>
       <c r="G16" t="n">
-        <v>33123</v>
+        <v>33167</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="O16" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P16" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Q16" t="n">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="R16" t="n">
-        <v>29479</v>
+        <v>29519</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:48</t>
+          <t>2026-10-24 19:07:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:50</t>
+          <t>2026-10-24 19:07:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80942</v>
+        <v>4.80957</v>
       </c>
       <c r="G3" t="n">
-        <v>13821</v>
+        <v>13832</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>138</v>
       </c>
       <c r="Q3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R3" t="n">
-        <v>12854</v>
+        <v>12864</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:52</t>
+          <t>2026-10-24 19:07:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87469</v>
+        <v>3.87492</v>
       </c>
       <c r="G4" t="n">
-        <v>4884</v>
+        <v>4885</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>3028</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:55</t>
+          <t>2026-10-24 19:07:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83293</v>
+        <v>2.83232</v>
       </c>
       <c r="G5" t="n">
-        <v>3298</v>
+        <v>3304</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="O5" t="n">
         <v>165</v>
@@ -805,7 +805,7 @@
         <v>132</v>
       </c>
       <c r="R5" t="n">
-        <v>1319</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:57</t>
+          <t>2026-10-24 19:07:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.28796</v>
       </c>
       <c r="G6" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -877,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:59</t>
+          <t>2026-10-24 19:07:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98614</v>
+        <v>3.98589</v>
       </c>
       <c r="G7" t="n">
-        <v>3823</v>
+        <v>3826</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>421</v>
       </c>
       <c r="R7" t="n">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:02</t>
+          <t>2026-10-24 19:07:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:04</t>
+          <t>2026-10-24 19:07:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:07</t>
+          <t>2026-10-24 19:07:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:09</t>
+          <t>2026-10-24 19:07:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:11</t>
+          <t>2026-10-24 19:07:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70273</v>
+        <v>4.70408</v>
       </c>
       <c r="G12" t="n">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>64</v>
       </c>
       <c r="Q12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2774</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:14</t>
+          <t>2026-10-24 19:07:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:16</t>
+          <t>2026-10-24 19:07:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.47177</v>
+        <v>3.47036</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:18</t>
+          <t>2026-10-24 19:08:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-23 20:09:20</t>
+          <t>2026-10-24 19:08:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73775</v>
+        <v>4.7378</v>
       </c>
       <c r="G16" t="n">
-        <v>33167</v>
+        <v>33185</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>332</v>
       </c>
       <c r="P16" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Q16" t="n">
         <v>1327</v>
       </c>
       <c r="R16" t="n">
-        <v>29519</v>
+        <v>29535</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:30</t>
+          <t>2026-10-25 19:31:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:32</t>
+          <t>2026-10-25 19:31:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80957</v>
+        <v>4.80968</v>
       </c>
       <c r="G3" t="n">
-        <v>13832</v>
+        <v>13845</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>277</v>
       </c>
       <c r="R3" t="n">
-        <v>12864</v>
+        <v>12876</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:35</t>
+          <t>2026-10-25 19:31:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87492</v>
+        <v>3.87433</v>
       </c>
       <c r="G4" t="n">
-        <v>4885</v>
+        <v>4886</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:37</t>
+          <t>2026-10-25 19:31:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83232</v>
+        <v>2.83132</v>
       </c>
       <c r="G5" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="O5" t="n">
         <v>165</v>
@@ -805,7 +805,7 @@
         <v>132</v>
       </c>
       <c r="R5" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:40</t>
+          <t>2026-10-25 19:31:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:42</t>
+          <t>2026-10-25 19:31:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98589</v>
+        <v>3.98537</v>
       </c>
       <c r="G7" t="n">
-        <v>3826</v>
+        <v>3828</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O7" t="n">
         <v>153</v>
@@ -949,7 +949,7 @@
         <v>421</v>
       </c>
       <c r="R7" t="n">
-        <v>2410</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:45</t>
+          <t>2026-10-25 19:31:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:47</t>
+          <t>2026-10-25 19:31:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:49</t>
+          <t>2026-10-25 19:31:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:52</t>
+          <t>2026-10-25 19:31:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:54</t>
+          <t>2026-10-25 19:31:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70408</v>
+        <v>4.70425</v>
       </c>
       <c r="G12" t="n">
-        <v>3190</v>
+        <v>3192</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2775</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:57</t>
+          <t>2026-10-25 19:31:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:59</t>
+          <t>2026-10-25 19:32:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 19:08:02</t>
+          <t>2026-10-25 19:32:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 19:08:04</t>
+          <t>2026-10-25 19:32:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7378</v>
+        <v>4.7374</v>
       </c>
       <c r="G16" t="n">
-        <v>33185</v>
+        <v>33199</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="O16" t="n">
         <v>332</v>
@@ -1594,10 +1594,10 @@
         <v>664</v>
       </c>
       <c r="Q16" t="n">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="R16" t="n">
-        <v>29535</v>
+        <v>29547</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:30</t>
+          <t>2026-10-26 21:15:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:33</t>
+          <t>2026-10-26 21:15:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80968</v>
+        <v>4.80943</v>
       </c>
       <c r="G3" t="n">
-        <v>13845</v>
+        <v>13853</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q3" t="n">
         <v>277</v>
       </c>
       <c r="R3" t="n">
-        <v>12876</v>
+        <v>12883</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:35</t>
+          <t>2026-10-26 21:15:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:38</t>
+          <t>2026-10-26 21:15:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83132</v>
+        <v>2.83107</v>
       </c>
       <c r="G5" t="n">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>132</v>
       </c>
       <c r="R5" t="n">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:40</t>
+          <t>2026-10-26 21:15:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:43</t>
+          <t>2026-10-26 21:15:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:45</t>
+          <t>2026-10-26 21:15:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:47</t>
+          <t>2026-10-26 21:15:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:50</t>
+          <t>2026-10-26 21:15:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:53</t>
+          <t>2026-10-26 21:15:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.57692</v>
+        <v>2.54717</v>
       </c>
       <c r="G11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:55</t>
+          <t>2026-10-26 21:15:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70425</v>
+        <v>4.70561</v>
       </c>
       <c r="G12" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2777</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:57</t>
+          <t>2026-10-26 21:15:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 19:32:00</t>
+          <t>2026-10-26 21:15:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.47036</v>
+        <v>3.47638</v>
       </c>
       <c r="G14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 19:32:02</t>
+          <t>2026-10-26 21:15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-25 19:32:05</t>
+          <t>2026-10-26 21:15:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7374</v>
+        <v>4.73719</v>
       </c>
       <c r="G16" t="n">
-        <v>33199</v>
+        <v>33208</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1328</v>
       </c>
       <c r="R16" t="n">
-        <v>29547</v>
+        <v>29555</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:16</t>
+          <t>2026-10-27 21:02:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>September 20, 2026</t>
+          <t>October 27, 2026</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:18</t>
+          <t>2026-10-27 21:02:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80943</v>
+        <v>4.8093</v>
       </c>
       <c r="G3" t="n">
-        <v>13853</v>
+        <v>13865</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>277</v>
       </c>
       <c r="R3" t="n">
-        <v>12883</v>
+        <v>12894</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:20</t>
+          <t>2026-10-27 21:02:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:22</t>
+          <t>2026-10-27 21:02:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83107</v>
+        <v>2.83177</v>
       </c>
       <c r="G5" t="n">
-        <v>3309</v>
+        <v>3311</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="O5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P5" t="n">
         <v>99</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:25</t>
+          <t>2026-10-27 21:02:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.28796</v>
+        <v>3.27604</v>
       </c>
       <c r="G6" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>65</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:27</t>
+          <t>2026-10-27 21:02:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98537</v>
+        <v>3.98512</v>
       </c>
       <c r="G7" t="n">
-        <v>3828</v>
+        <v>3830</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>153</v>
       </c>
       <c r="P7" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q7" t="n">
         <v>421</v>
       </c>
       <c r="R7" t="n">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:29</t>
+          <t>2026-10-27 21:02:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:31</t>
+          <t>2026-10-27 21:02:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:34</t>
+          <t>2026-10-27 21:02:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:36</t>
+          <t>2026-10-27 21:02:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:38</t>
+          <t>2026-10-27 21:02:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70561</v>
+        <v>4.70553</v>
       </c>
       <c r="G12" t="n">
-        <v>3193</v>
+        <v>3199</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2778</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:41</t>
+          <t>2026-10-27 21:02:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:43</t>
+          <t>2026-10-27 21:02:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.47638</v>
+        <v>3.48617</v>
       </c>
       <c r="G14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>October 22, 2026</t>
+          <t>October 27, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:45</t>
+          <t>2026-10-27 21:02:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:47</t>
+          <t>2026-10-27 21:02:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73719</v>
+        <v>4.73672</v>
       </c>
       <c r="G16" t="n">
-        <v>33208</v>
+        <v>33232</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="O16" t="n">
         <v>332</v>
       </c>
       <c r="P16" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="Q16" t="n">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="R16" t="n">
-        <v>29555</v>
+        <v>29576</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:23</t>
+          <t>2026-10-28 21:24:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:25</t>
+          <t>2026-10-28 21:24:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8093</v>
+        <v>4.80895</v>
       </c>
       <c r="G3" t="n">
-        <v>13865</v>
+        <v>13881</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>139</v>
       </c>
       <c r="Q3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R3" t="n">
-        <v>12894</v>
+        <v>12909</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:27</t>
+          <t>2026-10-28 21:24:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87433</v>
+        <v>3.87457</v>
       </c>
       <c r="G4" t="n">
-        <v>4886</v>
+        <v>4887</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>3029</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:29</t>
+          <t>2026-10-28 21:24:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83177</v>
+        <v>2.83198</v>
       </c>
       <c r="G5" t="n">
-        <v>3311</v>
+        <v>3315</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="O5" t="n">
         <v>166</v>
@@ -802,10 +802,10 @@
         <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R5" t="n">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:32</t>
+          <t>2026-10-28 21:24:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.27604</v>
+        <v>3.25521</v>
       </c>
       <c r="G6" t="n">
         <v>192</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>October 28, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:34</t>
+          <t>2026-10-28 21:24:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98512</v>
+        <v>3.98721</v>
       </c>
       <c r="G7" t="n">
-        <v>3830</v>
+        <v>3832</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>192</v>
       </c>
       <c r="Q7" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R7" t="n">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:36</t>
+          <t>2026-10-28 21:24:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:38</t>
+          <t>2026-10-28 21:24:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:41</t>
+          <t>2026-10-28 21:24:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:43</t>
+          <t>2026-10-28 21:24:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:45</t>
+          <t>2026-10-28 21:24:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70553</v>
+        <v>4.70381</v>
       </c>
       <c r="G12" t="n">
-        <v>3199</v>
+        <v>3204</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2783</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:48</t>
+          <t>2026-10-28 21:24:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:50</t>
+          <t>2026-10-28 21:24:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.48617</v>
+        <v>3.4786</v>
       </c>
       <c r="G14" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:52</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:54</t>
+          <t>2026-10-28 21:24:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73672</v>
+        <v>4.73675</v>
       </c>
       <c r="G16" t="n">
-        <v>33232</v>
+        <v>33254</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="O16" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P16" t="n">
         <v>665</v>
       </c>
       <c r="Q16" t="n">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="R16" t="n">
-        <v>29576</v>
+        <v>29596</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:01</t>
+          <t>2026-10-29 21:29:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.61628</v>
+        <v>4.6185</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:03</t>
+          <t>2026-10-29 21:29:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80895</v>
+        <v>4.80883</v>
       </c>
       <c r="G3" t="n">
-        <v>13881</v>
+        <v>13888</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.5</t>
+          <t>4.46.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,11 +645,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>October 16, 2026</t>
+          <t>October 29, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O3" t="n">
         <v>139</v>
@@ -661,7 +661,7 @@
         <v>278</v>
       </c>
       <c r="R3" t="n">
-        <v>12909</v>
+        <v>12916</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:06</t>
+          <t>2026-10-29 21:29:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:08</t>
+          <t>2026-10-29 21:29:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83198</v>
+        <v>2.83268</v>
       </c>
       <c r="G5" t="n">
-        <v>3315</v>
+        <v>3317</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="O5" t="n">
         <v>166</v>
       </c>
       <c r="P5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
         <v>133</v>
       </c>
       <c r="R5" t="n">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:11</t>
+          <t>2026-10-29 21:29:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25521</v>
+        <v>3.28283</v>
       </c>
       <c r="G6" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
@@ -874,10 +874,10 @@
         <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:13</t>
+          <t>2026-10-29 21:29:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98721</v>
+        <v>3.9867</v>
       </c>
       <c r="G7" t="n">
-        <v>3832</v>
+        <v>3834</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O7" t="n">
         <v>153</v>
@@ -949,7 +949,7 @@
         <v>422</v>
       </c>
       <c r="R7" t="n">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:15</t>
+          <t>2026-10-29 21:29:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:18</t>
+          <t>2026-10-29 21:29:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:20</t>
+          <t>2026-10-29 21:29:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:22</t>
+          <t>2026-10-29 21:29:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:25</t>
+          <t>2026-10-29 21:29:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70381</v>
+        <v>4.70493</v>
       </c>
       <c r="G12" t="n">
-        <v>3204</v>
+        <v>3206</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2787</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:27</t>
+          <t>2026-10-29 21:29:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.99485</v>
+        <v>3.98973</v>
       </c>
       <c r="G13" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="O13" t="n">
         <v>23</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="n">
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:29</t>
+          <t>2026-10-29 21:29:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4786</v>
+        <v>3.4845</v>
       </c>
       <c r="G14" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-29 21:29:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:34</t>
+          <t>2026-10-29 21:29:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73675</v>
+        <v>4.7365</v>
       </c>
       <c r="G16" t="n">
-        <v>33254</v>
+        <v>33267</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="O16" t="n">
         <v>333</v>
@@ -1594,10 +1594,10 @@
         <v>665</v>
       </c>
       <c r="Q16" t="n">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="R16" t="n">
-        <v>29596</v>
+        <v>29608</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:15</t>
+          <t>2026-10-30 21:10:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:17</t>
+          <t>2026-10-30 21:10:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.80883</v>
+        <v>4.80891</v>
       </c>
       <c r="G3" t="n">
-        <v>13888</v>
+        <v>13895</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>278</v>
       </c>
       <c r="R3" t="n">
-        <v>12916</v>
+        <v>12922</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:19</t>
+          <t>2026-10-30 21:10:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:21</t>
+          <t>2026-10-30 21:10:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.83268</v>
+        <v>2.83338</v>
       </c>
       <c r="G5" t="n">
-        <v>3317</v>
+        <v>3319</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="O5" t="n">
         <v>166</v>
@@ -805,7 +805,7 @@
         <v>133</v>
       </c>
       <c r="R5" t="n">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:24</t>
+          <t>2026-10-30 21:10:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.28283</v>
+        <v>3.31188</v>
       </c>
       <c r="G6" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>67</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
         <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:26</t>
+          <t>2026-10-30 21:10:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9867</v>
+        <v>3.98697</v>
       </c>
       <c r="G7" t="n">
-        <v>3834</v>
+        <v>3837</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>422</v>
       </c>
       <c r="R7" t="n">
-        <v>2415</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:28</t>
+          <t>2026-10-30 21:10:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:30</t>
+          <t>2026-10-30 21:10:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:32</t>
+          <t>2026-10-30 21:10:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:35</t>
+          <t>2026-10-30 21:10:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54717</v>
+        <v>2.51852</v>
       </c>
       <c r="G11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>September 02, 2026</t>
+          <t>October 29, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:37</t>
+          <t>2026-10-30 21:10:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70493</v>
+        <v>4.702</v>
       </c>
       <c r="G12" t="n">
-        <v>3206</v>
+        <v>3208</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>160</v>
       </c>
       <c r="R12" t="n">
-        <v>2789</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:39</t>
+          <t>2026-10-30 21:10:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:41</t>
+          <t>2026-10-30 21:10:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4845</v>
+        <v>3.49035</v>
       </c>
       <c r="G14" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:44</t>
+          <t>2026-10-30 21:11:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:46</t>
+          <t>2026-10-30 21:11:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7365</v>
+        <v>4.7363</v>
       </c>
       <c r="G16" t="n">
-        <v>33267</v>
+        <v>33281</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>333</v>
       </c>
       <c r="P16" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Q16" t="n">
         <v>1331</v>
       </c>
       <c r="R16" t="n">
-        <v>29608</v>
+        <v>29620</v>
       </c>
     </row>
   </sheetData>
